--- a/planilhas/contratos_locacao.xlsx
+++ b/planilhas/contratos_locacao.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$BJ$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$BJ$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$BJ$50</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="462">
   <si>
     <t>Contratos de Locação</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em sábado, 6 de junho de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em segunda-feira, 22 de junho de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Ano Modelo</t>
@@ -232,199 +232,406 @@
     <t/>
   </si>
   <si>
+    <t>9C2KC2500RR115224</t>
+  </si>
+  <si>
+    <t>SEGCOMP</t>
+  </si>
+  <si>
+    <t>JOEL LOPES</t>
+  </si>
+  <si>
+    <t>CTO-1038</t>
+  </si>
+  <si>
+    <t>NOVO CONTRATO</t>
+  </si>
+  <si>
+    <t>LOC-1038-3/24</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>41.153.812/0001-54</t>
+  </si>
+  <si>
+    <t>BPOFINANCEIRO@GRUPOECOMP.COM.BR</t>
+  </si>
+  <si>
+    <t>2.000 KM</t>
+  </si>
+  <si>
+    <t>MOTO</t>
+  </si>
+  <si>
+    <t>R$ 0,00</t>
+  </si>
+  <si>
+    <t>EM UTILIZAÇÃO</t>
+  </si>
+  <si>
+    <t>CG 160 START</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>1412406037</t>
+  </si>
+  <si>
+    <t>EM ANDAMENTO</t>
+  </si>
+  <si>
+    <t>FATURAR</t>
+  </si>
+  <si>
+    <t>(84) 30133030</t>
+  </si>
+  <si>
+    <t>PESSOA JURÍDICA</t>
+  </si>
+  <si>
+    <t>TERCEIRIZAÇÃO DE FROTA</t>
+  </si>
+  <si>
+    <t>ATIVUZ VEÍCULOS</t>
+  </si>
+  <si>
+    <t>RQI-7A69</t>
+  </si>
+  <si>
+    <t>PRINCIPAL</t>
+  </si>
+  <si>
+    <t>9C2KC2500RR115213</t>
+  </si>
+  <si>
+    <t>LOC-1038-4/24</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>1412409583</t>
+  </si>
+  <si>
+    <t>RQI-7A89</t>
+  </si>
+  <si>
+    <t>9C2KD0810RR165173</t>
+  </si>
+  <si>
+    <t>LOC-1038-2/24</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>NXR 160 BROS ESDD FLEXONE</t>
+  </si>
+  <si>
+    <t>1413837562</t>
+  </si>
+  <si>
+    <t>RQJ-7H29</t>
+  </si>
+  <si>
     <t>9BWAG45U9PT049067</t>
   </si>
   <si>
-    <t>SEGCOMP</t>
-  </si>
-  <si>
-    <t>JOEL LOPES</t>
-  </si>
-  <si>
-    <t>CTO-1038</t>
-  </si>
-  <si>
-    <t>NOVO CONTRATO</t>
-  </si>
-  <si>
     <t>LOC-1038-1/24</t>
   </si>
   <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>41.153.812/0001-54</t>
-  </si>
-  <si>
-    <t>BPOFINANCEIRO@GRUPOECOMP.COM.BR</t>
-  </si>
-  <si>
-    <t>2.000 KM</t>
+    <t>53</t>
   </si>
   <si>
     <t>HATCH</t>
   </si>
   <si>
-    <t>R$ 0,00</t>
-  </si>
-  <si>
-    <t>EM UTILIZAÇÃO</t>
-  </si>
-  <si>
     <t>GOL 1.0 FLEX 12V 5P</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>1317566103</t>
   </si>
   <si>
-    <t>EM ANDAMENTO</t>
-  </si>
-  <si>
-    <t>FATURAR</t>
-  </si>
-  <si>
-    <t>(84) 30133030</t>
-  </si>
-  <si>
-    <t>PESSOA JURÍDICA</t>
-  </si>
-  <si>
-    <t>TERCEIRIZAÇÃO DE FROTA</t>
-  </si>
-  <si>
-    <t>ATIVUZ VEÍCULOS</t>
-  </si>
-  <si>
     <t>EGX-2E31</t>
   </si>
   <si>
-    <t>PRINCIPAL</t>
-  </si>
-  <si>
-    <t>9C2KD0810RR165173</t>
-  </si>
-  <si>
-    <t>LOC-1038-2/24</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>MOTO</t>
-  </si>
-  <si>
-    <t>NXR 160 BROS ESDD FLEXONE</t>
-  </si>
-  <si>
-    <t>1413837562</t>
-  </si>
-  <si>
-    <t>RQJ-7H29</t>
-  </si>
-  <si>
-    <t>9C2KC2500RR115224</t>
-  </si>
-  <si>
-    <t>LOC-1038-3/24</t>
+    <t>122.136.017-55</t>
+  </si>
+  <si>
+    <t>9BWAG45U9MT107528</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>CTO-1032</t>
+  </si>
+  <si>
+    <t>LOC-1032-1/1</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>EM MANUTENÇÃO</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1253794178</t>
+  </si>
+  <si>
+    <t>84 99837-3901</t>
+  </si>
+  <si>
+    <t>PESSOA FÍSICA</t>
+  </si>
+  <si>
+    <t>MOTORISTA DE APLICATIVO</t>
+  </si>
+  <si>
+    <t>RGE-7H03</t>
+  </si>
+  <si>
+    <t>480.697.874-49</t>
+  </si>
+  <si>
+    <t>9BWDB45U5KT135660</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>CTO-1022</t>
+  </si>
+  <si>
+    <t>LOC-1022-1/4</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>SEDAN</t>
+  </si>
+  <si>
+    <t>VOYAGE 1.6 MSI FLEX 8V 4P</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1189763750</t>
+  </si>
+  <si>
+    <t>(84) 996369127</t>
+  </si>
+  <si>
+    <t>QGU-1H54</t>
+  </si>
+  <si>
+    <t>117.936.764-29</t>
+  </si>
+  <si>
+    <t>9BWDG45U7PT091086</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>CTO-1016</t>
+  </si>
+  <si>
+    <t>LOC-1016-1/5</t>
+  </si>
+  <si>
+    <t>VOYAGE 1.0 FLEX 12V 4P</t>
+  </si>
+  <si>
+    <t>1329648010</t>
+  </si>
+  <si>
+    <t>84 98890-2831</t>
+  </si>
+  <si>
+    <t>ECZ-8C02</t>
+  </si>
+  <si>
+    <t>069.054.054-00</t>
+  </si>
+  <si>
+    <t>9BWDG45U8NT005796</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>CTO-1024</t>
+  </si>
+  <si>
+    <t>LOC-1024-1/7</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1253652063</t>
+  </si>
+  <si>
+    <t>(84) 981911956</t>
+  </si>
+  <si>
+    <t>RMK-2H75</t>
+  </si>
+  <si>
+    <t>071.198.454-97</t>
+  </si>
+  <si>
+    <t>9BWDB45U9KT124595</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>CTO-1015</t>
+  </si>
+  <si>
+    <t>LOC-1015-1/2</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1190075218</t>
+  </si>
+  <si>
+    <t>(84) 981397610</t>
+  </si>
+  <si>
+    <t>QSE-8E63</t>
+  </si>
+  <si>
+    <t>101.093.374-41</t>
+  </si>
+  <si>
+    <t>9BWDG45U3PT091098</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>CTO-1011</t>
+  </si>
+  <si>
+    <t>LOC-1011-1/9</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>CG 160 START</t>
-  </si>
-  <si>
-    <t>1412406037</t>
-  </si>
-  <si>
-    <t>RQI-7A69</t>
-  </si>
-  <si>
-    <t>9C2KC2500RR115213</t>
-  </si>
-  <si>
-    <t>LOC-1038-4/24</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>1412409583</t>
-  </si>
-  <si>
-    <t>RQI-7A89</t>
-  </si>
-  <si>
-    <t>122.136.017-55</t>
-  </si>
-  <si>
-    <t>9BWAG45U9MT107528</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>CTO-1032</t>
-  </si>
-  <si>
-    <t>LOC-1032-1/1</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>1253794178</t>
-  </si>
-  <si>
-    <t>84 99837-3901</t>
-  </si>
-  <si>
-    <t>PESSOA FÍSICA</t>
-  </si>
-  <si>
-    <t>MOTORISTA DE APLICATIVO</t>
-  </si>
-  <si>
-    <t>RGE-7H03</t>
-  </si>
-  <si>
-    <t>480.697.874-49</t>
-  </si>
-  <si>
-    <t>9BWDB45U5KT135660</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>CTO-1022</t>
-  </si>
-  <si>
-    <t>LOC-1022-1/4</t>
-  </si>
-  <si>
-    <t>SEDAN</t>
-  </si>
-  <si>
-    <t>VOYAGE 1.6 MSI FLEX 8V 4P</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1189763750</t>
-  </si>
-  <si>
-    <t>(84) 996369127</t>
-  </si>
-  <si>
-    <t>QGU-1H54</t>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1329647642</t>
+  </si>
+  <si>
+    <t>(84) 987180189</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>END-0I15</t>
+  </si>
+  <si>
+    <t>120.205.544-37</t>
+  </si>
+  <si>
+    <t>9BWAG45UXJT141960</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>CTO-1028</t>
+  </si>
+  <si>
+    <t>LOC-1028-1/8</t>
+  </si>
+  <si>
+    <t>GOL TRENDLINE 1.0 T.FLEX 12V 5P</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1149589393</t>
+  </si>
+  <si>
+    <t>84 99616-2852</t>
+  </si>
+  <si>
+    <t>QGX-7353</t>
+  </si>
+  <si>
+    <t>009.554.944-78</t>
+  </si>
+  <si>
+    <t>9BWDG45U1PT010258</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>CTO-1023</t>
+  </si>
+  <si>
+    <t>LOC-1023-1/13</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>01298307187</t>
+  </si>
+  <si>
+    <t>84 99212-8471</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>GIY-6G96</t>
+  </si>
+  <si>
+    <t>705.762.454-96</t>
+  </si>
+  <si>
+    <t>9BWDG45UXPT092720</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>CTO-1029</t>
+  </si>
+  <si>
+    <t>LOC-1029-1/2</t>
+  </si>
+  <si>
+    <t>1329889310</t>
+  </si>
+  <si>
+    <t>(84) 921697458</t>
+  </si>
+  <si>
+    <t>EXF-1F14</t>
   </si>
   <si>
     <t>790.887.914-49</t>
@@ -442,12 +649,6 @@
     <t>LOC-1018-1/2</t>
   </si>
   <si>
-    <t>VOYAGE 1.0 FLEX 12V 4P</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>01329662196</t>
   </si>
   <si>
@@ -457,204 +658,6 @@
     <t>EMQ-6C26</t>
   </si>
   <si>
-    <t>009.554.944-78</t>
-  </si>
-  <si>
-    <t>9BWDG45U1PT010258</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>CTO-1023</t>
-  </si>
-  <si>
-    <t>LOC-1023-1/13</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>01298307187</t>
-  </si>
-  <si>
-    <t>84 99212-8471</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t>GIY-6G96</t>
-  </si>
-  <si>
-    <t>117.936.764-29</t>
-  </si>
-  <si>
-    <t>9BWDG45U7PT091086</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>CTO-1016</t>
-  </si>
-  <si>
-    <t>LOC-1016-1/5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>1329648010</t>
-  </si>
-  <si>
-    <t>84 98890-2831</t>
-  </si>
-  <si>
-    <t>ECZ-8C02</t>
-  </si>
-  <si>
-    <t>101.093.374-41</t>
-  </si>
-  <si>
-    <t>9BWDG45U3PT091098</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>CTO-1011</t>
-  </si>
-  <si>
-    <t>LOC-1011-1/9</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>1329647642</t>
-  </si>
-  <si>
-    <t>(84) 987180189</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>END-0I15</t>
-  </si>
-  <si>
-    <t>705.762.454-96</t>
-  </si>
-  <si>
-    <t>9BWDG45UXPT092720</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>CTO-1029</t>
-  </si>
-  <si>
-    <t>LOC-1029-1/2</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1329889310</t>
-  </si>
-  <si>
-    <t>(84) 921697458</t>
-  </si>
-  <si>
-    <t>EXF-1F14</t>
-  </si>
-  <si>
-    <t>120.205.544-37</t>
-  </si>
-  <si>
-    <t>9BWAG45UXJT141960</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>CTO-1028</t>
-  </si>
-  <si>
-    <t>LOC-1028-1/8</t>
-  </si>
-  <si>
-    <t>GOL TRENDLINE 1.0 T.FLEX 12V 5P</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>1149589393</t>
-  </si>
-  <si>
-    <t>84 99616-2852</t>
-  </si>
-  <si>
-    <t>QGX-7353</t>
-  </si>
-  <si>
-    <t>069.054.054-00</t>
-  </si>
-  <si>
-    <t>9BWDG45U8NT005796</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>CTO-1024</t>
-  </si>
-  <si>
-    <t>LOC-1024-1/7</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>1253652063</t>
-  </si>
-  <si>
-    <t>(84) 981911956</t>
-  </si>
-  <si>
-    <t>RMK-2H75</t>
-  </si>
-  <si>
-    <t>071.198.454-97</t>
-  </si>
-  <si>
-    <t>9BWDB45U9KT124595</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>CTO-1015</t>
-  </si>
-  <si>
-    <t>LOC-1015-1/2</t>
-  </si>
-  <si>
-    <t>1190075218</t>
-  </si>
-  <si>
-    <t>(84) 981397610</t>
-  </si>
-  <si>
-    <t>QSE-8E63</t>
-  </si>
-  <si>
     <t>017.712.914-00</t>
   </si>
   <si>
@@ -694,7 +697,7 @@
     <t>LOC-1017-1/2</t>
   </si>
   <si>
-    <t>30</t>
+    <t>46</t>
   </si>
   <si>
     <t>1239198733</t>
@@ -721,9 +724,6 @@
     <t>LOC-1010-1/9</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>1253118830</t>
   </si>
   <si>
@@ -733,6 +733,33 @@
     <t>RGE-5D51</t>
   </si>
   <si>
+    <t>092.354.354-63</t>
+  </si>
+  <si>
+    <t>9BWDB45U1LT065429</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>CTO-1004</t>
+  </si>
+  <si>
+    <t>LOC-1004-1/5</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>1206436686</t>
+  </si>
+  <si>
+    <t>84 92148-9407</t>
+  </si>
+  <si>
+    <t>QGS-6G16</t>
+  </si>
+  <si>
     <t>014.010.004-01</t>
   </si>
   <si>
@@ -748,7 +775,7 @@
     <t>LOC-1006-1/12</t>
   </si>
   <si>
-    <t>EM MANUTENÇÃO</t>
+    <t>6</t>
   </si>
   <si>
     <t>12</t>
@@ -763,30 +790,6 @@
     <t>RGE-7G92</t>
   </si>
   <si>
-    <t>092.354.354-63</t>
-  </si>
-  <si>
-    <t>9BWDB45U1LT065429</t>
-  </si>
-  <si>
-    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
-  </si>
-  <si>
-    <t>CTO-1004</t>
-  </si>
-  <si>
-    <t>LOC-1004-1/5</t>
-  </si>
-  <si>
-    <t>1206436686</t>
-  </si>
-  <si>
-    <t>84 92148-9407</t>
-  </si>
-  <si>
-    <t>QGS-6G16</t>
-  </si>
-  <si>
     <t>100.144.684-41</t>
   </si>
   <si>
@@ -829,7 +832,7 @@
     <t>LOC-1043-1/12</t>
   </si>
   <si>
-    <t>43</t>
+    <t>59</t>
   </si>
   <si>
     <t>1319762945</t>
@@ -856,7 +859,7 @@
     <t>LOC-1047-1/12</t>
   </si>
   <si>
-    <t>23</t>
+    <t>39</t>
   </si>
   <si>
     <t>1327877853</t>
@@ -931,10 +934,7 @@
     <t>LOC-1052-1/3</t>
   </si>
   <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>154</t>
   </si>
   <si>
     <t>01296669901</t>
@@ -961,7 +961,7 @@
     <t>LOC-1056-1/12</t>
   </si>
   <si>
-    <t>53</t>
+    <t>69</t>
   </si>
   <si>
     <t>1318410840</t>
@@ -985,7 +985,7 @@
     <t>LOC-1060-1/12</t>
   </si>
   <si>
-    <t>67</t>
+    <t>83</t>
   </si>
   <si>
     <t>23.802.049/0001-63</t>
@@ -1015,7 +1015,7 @@
     <t>LOC-1063-1/12</t>
   </si>
   <si>
-    <t>68</t>
+    <t>84</t>
   </si>
   <si>
     <t>01327467981</t>
@@ -1069,7 +1069,7 @@
     <t>LOC-1067-1/12</t>
   </si>
   <si>
-    <t>80</t>
+    <t>96</t>
   </si>
   <si>
     <t>POLO TRACK 1.0 FLEX 12V 5P</t>
@@ -1096,204 +1096,183 @@
     <t>LOC-1068-1/12</t>
   </si>
   <si>
-    <t>22</t>
+    <t>38</t>
   </si>
   <si>
     <t>1325953650</t>
   </si>
   <si>
+    <t>ECM-1C93</t>
+  </si>
+  <si>
+    <t>704.631.134-03</t>
+  </si>
+  <si>
+    <t>9BWDB45U7LT066973</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>CTO-1070</t>
+  </si>
+  <si>
+    <t>LOC-1070-1/12</t>
+  </si>
+  <si>
+    <t>1207486415</t>
+  </si>
+  <si>
+    <t>QGT-1D67</t>
+  </si>
+  <si>
+    <t>9BWAG45U4MT005800</t>
+  </si>
+  <si>
+    <t>NEW CHARGER</t>
+  </si>
+  <si>
+    <t>CTO-1073</t>
+  </si>
+  <si>
+    <t>LOC-1073-1/2</t>
+  </si>
+  <si>
+    <t>46.346.152/0001-41</t>
+  </si>
+  <si>
+    <t>1225842635</t>
+  </si>
+  <si>
+    <t>QGT-9D86</t>
+  </si>
+  <si>
+    <t>009.896.264-74</t>
+  </si>
+  <si>
+    <t>9BWAG45U4MT107453</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>CTO-1071</t>
+  </si>
+  <si>
+    <t>LOC-1071-1/12</t>
+  </si>
+  <si>
+    <t>1253794054</t>
+  </si>
+  <si>
+    <t>RGE-7H02</t>
+  </si>
+  <si>
+    <t>059.640.564-23</t>
+  </si>
+  <si>
+    <t>92VCE4CC9VK025626</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>CTO-1075</t>
+  </si>
+  <si>
+    <t>LOC-1075-1/12</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>DOLPHIN MINI (ELÉTRICO)</t>
+  </si>
+  <si>
+    <t>01489393657</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>TSW-3H63</t>
+  </si>
+  <si>
+    <t>097.034.444-90</t>
+  </si>
+  <si>
+    <t>9BWAG45U5LT080519</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>CTO-1077</t>
+  </si>
+  <si>
+    <t>LOC-1077-1/4</t>
+  </si>
+  <si>
+    <t>1214268843</t>
+  </si>
+  <si>
+    <t>(84) 981787788</t>
+  </si>
+  <si>
+    <t>QGW-2B89</t>
+  </si>
+  <si>
+    <t>105.001.424-32</t>
+  </si>
+  <si>
+    <t>9BWAB45U2JT067951</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>CTO-1078</t>
+  </si>
+  <si>
+    <t>LOC-1078-1/12</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>GOL (NOVO) 1.6 MI TOTAL FLEX 8V 4P</t>
+  </si>
+  <si>
+    <t>01136312835</t>
+  </si>
+  <si>
+    <t>QGO-2H58</t>
+  </si>
+  <si>
+    <t>077.732.684-10</t>
+  </si>
+  <si>
+    <t>9BWDG45U9PT071678</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>CTO-1082</t>
+  </si>
+  <si>
+    <t>LOC-1082-1/8</t>
+  </si>
+  <si>
+    <t>01323779938</t>
+  </si>
+  <si>
+    <t>(84) 981675906</t>
+  </si>
+  <si>
     <t>CONFORME UNIDADE DO VEÍCULO</t>
   </si>
   <si>
-    <t>ECM-1C93</t>
-  </si>
-  <si>
-    <t>704.631.134-03</t>
-  </si>
-  <si>
-    <t>9BWDB45U7LT066973</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>CTO-1070</t>
-  </si>
-  <si>
-    <t>LOC-1070-1/12</t>
-  </si>
-  <si>
-    <t>1207486415</t>
-  </si>
-  <si>
-    <t>QGT-1D67</t>
-  </si>
-  <si>
-    <t>9BWAG45U4MT005800</t>
-  </si>
-  <si>
-    <t>NEW CHARGER</t>
-  </si>
-  <si>
-    <t>CTO-1073</t>
-  </si>
-  <si>
-    <t>LOC-1073-1/2</t>
-  </si>
-  <si>
-    <t>46.346.152/0001-41</t>
-  </si>
-  <si>
-    <t>1225842635</t>
-  </si>
-  <si>
-    <t>QGT-9D86</t>
-  </si>
-  <si>
-    <t>009.896.264-74</t>
-  </si>
-  <si>
-    <t>9BWAG45U4MT107453</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>CTO-1071</t>
-  </si>
-  <si>
-    <t>LOC-1071-1/12</t>
-  </si>
-  <si>
-    <t>1253794054</t>
-  </si>
-  <si>
-    <t>RGE-7H02</t>
-  </si>
-  <si>
-    <t>059.640.564-23</t>
-  </si>
-  <si>
-    <t>92VCE4CC9VK025626</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>CTO-1075</t>
-  </si>
-  <si>
-    <t>LOC-1075-1/12</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>DOLPHIN MINI (ELÉTRICO)</t>
-  </si>
-  <si>
-    <t>01489393657</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>TSW-3H63</t>
-  </si>
-  <si>
-    <t>097.034.444-90</t>
-  </si>
-  <si>
-    <t>9BWAG45U5LT080519</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>CTO-1077</t>
-  </si>
-  <si>
-    <t>LOC-1077-1/4</t>
-  </si>
-  <si>
-    <t>1214268843</t>
-  </si>
-  <si>
-    <t>(84) 981787788</t>
-  </si>
-  <si>
-    <t>QGW-2B89</t>
-  </si>
-  <si>
-    <t>031.396.964-77</t>
-  </si>
-  <si>
-    <t>92VCE4CC1VK025636</t>
-  </si>
-  <si>
-    <t>ADRIANO TEOTONIO DA SILVA</t>
-  </si>
-  <si>
-    <t>CTO-1074</t>
-  </si>
-  <si>
-    <t>LOC-1074-1/12</t>
-  </si>
-  <si>
-    <t>01489400122</t>
-  </si>
-  <si>
-    <t>TSW-3I03</t>
-  </si>
-  <si>
-    <t>105.001.424-32</t>
-  </si>
-  <si>
-    <t>9BWAB45U2JT067951</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>CTO-1078</t>
-  </si>
-  <si>
-    <t>LOC-1078-1/12</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>GOL (NOVO) 1.6 MI TOTAL FLEX 8V 4P</t>
-  </si>
-  <si>
-    <t>01136312835</t>
-  </si>
-  <si>
-    <t>QGO-2H58</t>
-  </si>
-  <si>
-    <t>077.732.684-10</t>
-  </si>
-  <si>
-    <t>9BWDG45U9PT071678</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>CTO-1082</t>
-  </si>
-  <si>
-    <t>LOC-1082-1/8</t>
-  </si>
-  <si>
-    <t>01323779938</t>
-  </si>
-  <si>
-    <t>(84) 981675906</t>
-  </si>
-  <si>
     <t>ELY-4D83</t>
   </si>
   <si>
@@ -1333,7 +1312,7 @@
     <t>LOC-1079-1/12</t>
   </si>
   <si>
-    <t>19</t>
+    <t>35</t>
   </si>
   <si>
     <t>01489397822</t>
@@ -1427,6 +1406,9 @@
   </si>
   <si>
     <t>LOC-1084-1/8</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
   <si>
     <t>1327460677</t>
@@ -1591,7 +1573,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:BJ51"/>
+  <dimension ref="A1:BJ50"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1" style="1"/>
@@ -1865,10 +1847,10 @@
     </row>
     <row r="6">
       <c r="A6" s="7">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B6" s="7">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>65</v>
@@ -1940,13 +1922,13 @@
         <v>75</v>
       </c>
       <c r="Z6" s="10">
-        <v>260.55</v>
+        <v>65.58</v>
       </c>
       <c r="AA6" s="10">
         <v>0</v>
       </c>
       <c r="AB6" s="10">
-        <v>260.55</v>
+        <v>65.58</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>76</v>
@@ -1958,10 +1940,10 @@
         <v>45590.458333333336</v>
       </c>
       <c r="AF6" s="7">
-        <v>83783</v>
+        <v>18588</v>
       </c>
       <c r="AG6" s="9">
-        <v>46175.35753472222</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH6" s="6" t="s">
         <v>77</v>
@@ -1970,7 +1952,7 @@
         <v>78</v>
       </c>
       <c r="AJ6" s="11">
-        <v>0.04059829059829</v>
+        <v>0.042943797305276</v>
       </c>
       <c r="AK6" s="6" t="s">
         <v>79</v>
@@ -2000,7 +1982,7 @@
         <v>81</v>
       </c>
       <c r="AT6" s="7">
-        <v>4268</v>
+        <v>921</v>
       </c>
       <c r="AU6" s="6" t="s">
         <v>82</v>
@@ -2033,13 +2015,13 @@
         <v>0</v>
       </c>
       <c r="BE6" s="10">
-        <v>46800</v>
+        <v>18629</v>
       </c>
       <c r="BF6" s="10">
-        <v>1900</v>
+        <v>800</v>
       </c>
       <c r="BG6" s="10">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="BH6" s="6" t="s">
         <v>88</v>
@@ -2128,16 +2110,16 @@
         <v>75</v>
       </c>
       <c r="Z7" s="10">
-        <v>32.79</v>
+        <v>98.37</v>
       </c>
       <c r="AA7" s="10">
         <v>0</v>
       </c>
       <c r="AB7" s="10">
-        <v>32.79</v>
+        <v>98.37</v>
       </c>
       <c r="AC7" s="6" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AD7" s="6" t="s">
         <v>65</v>
@@ -2146,10 +2128,10 @@
         <v>45590.458333333336</v>
       </c>
       <c r="AF7" s="7">
-        <v>30242</v>
+        <v>15448</v>
       </c>
       <c r="AG7" s="9">
-        <v>46175.35753472222</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH7" s="6" t="s">
         <v>77</v>
@@ -2158,10 +2140,10 @@
         <v>78</v>
       </c>
       <c r="AJ7" s="11">
-        <v>0.113938473224458</v>
+        <v>0.042943797305276</v>
       </c>
       <c r="AK7" s="6" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="AL7" s="6" t="s">
         <v>65</v>
@@ -2185,10 +2167,10 @@
         <v>65</v>
       </c>
       <c r="AS7" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AT7" s="7">
-        <v>1540</v>
+        <v>765</v>
       </c>
       <c r="AU7" s="6" t="s">
         <v>82</v>
@@ -2221,19 +2203,19 @@
         <v>0</v>
       </c>
       <c r="BE7" s="10">
-        <v>7899</v>
+        <v>18629</v>
       </c>
       <c r="BF7" s="10">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="BG7" s="10">
-        <v>900</v>
+        <v>1600</v>
       </c>
       <c r="BH7" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="BI7" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="BJ7" s="6" t="s">
         <v>89</v>
@@ -2253,7 +2235,7 @@
         <v>65</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>65</v>
@@ -2277,7 +2259,7 @@
         <v>70</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>65</v>
@@ -2295,7 +2277,7 @@
         <v>65</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="T8" s="6" t="s">
         <v>73</v>
@@ -2316,16 +2298,16 @@
         <v>75</v>
       </c>
       <c r="Z8" s="10">
-        <v>65.58</v>
+        <v>32.79</v>
       </c>
       <c r="AA8" s="10">
         <v>0</v>
       </c>
       <c r="AB8" s="10">
-        <v>65.58</v>
+        <v>32.79</v>
       </c>
       <c r="AC8" s="6" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AD8" s="6" t="s">
         <v>65</v>
@@ -2334,10 +2316,10 @@
         <v>45590.458333333336</v>
       </c>
       <c r="AF8" s="7">
-        <v>18462</v>
+        <v>30542</v>
       </c>
       <c r="AG8" s="9">
-        <v>46175.35753472222</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH8" s="6" t="s">
         <v>77</v>
@@ -2346,10 +2328,10 @@
         <v>78</v>
       </c>
       <c r="AJ8" s="11">
-        <v>0.042943797305276</v>
+        <v>0.113938473224458</v>
       </c>
       <c r="AK8" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AL8" s="6" t="s">
         <v>65</v>
@@ -2373,10 +2355,10 @@
         <v>65</v>
       </c>
       <c r="AS8" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AT8" s="7">
-        <v>940</v>
+        <v>1514</v>
       </c>
       <c r="AU8" s="6" t="s">
         <v>82</v>
@@ -2409,19 +2391,19 @@
         <v>0</v>
       </c>
       <c r="BE8" s="10">
-        <v>18629</v>
+        <v>7899</v>
       </c>
       <c r="BF8" s="10">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="BG8" s="10">
-        <v>1600</v>
+        <v>900</v>
       </c>
       <c r="BH8" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="BI8" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="BJ8" s="6" t="s">
         <v>89</v>
@@ -2429,10 +2411,10 @@
     </row>
     <row r="9">
       <c r="A9" s="7">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B9" s="7">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>65</v>
@@ -2441,7 +2423,7 @@
         <v>65</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>65</v>
@@ -2465,7 +2447,7 @@
         <v>70</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N9" s="6" t="s">
         <v>65</v>
@@ -2483,7 +2465,7 @@
         <v>65</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>73</v>
@@ -2504,16 +2486,16 @@
         <v>75</v>
       </c>
       <c r="Z9" s="10">
-        <v>98.37</v>
+        <v>260.55</v>
       </c>
       <c r="AA9" s="10">
         <v>0</v>
       </c>
       <c r="AB9" s="10">
-        <v>98.37</v>
+        <v>260.55</v>
       </c>
       <c r="AC9" s="6" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="AD9" s="6" t="s">
         <v>65</v>
@@ -2522,10 +2504,10 @@
         <v>45590.458333333336</v>
       </c>
       <c r="AF9" s="7">
-        <v>15278</v>
+        <v>84171</v>
       </c>
       <c r="AG9" s="9">
-        <v>46176.41266203704</v>
+        <v>46181.609398148146</v>
       </c>
       <c r="AH9" s="6" t="s">
         <v>77</v>
@@ -2534,10 +2516,10 @@
         <v>78</v>
       </c>
       <c r="AJ9" s="11">
-        <v>0.042943797305276</v>
+        <v>0.04059829059829</v>
       </c>
       <c r="AK9" s="6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AL9" s="6" t="s">
         <v>65</v>
@@ -2564,7 +2546,7 @@
         <v>106</v>
       </c>
       <c r="AT9" s="7">
-        <v>778</v>
+        <v>4173</v>
       </c>
       <c r="AU9" s="6" t="s">
         <v>82</v>
@@ -2597,13 +2579,13 @@
         <v>0</v>
       </c>
       <c r="BE9" s="10">
-        <v>18629</v>
+        <v>46800</v>
       </c>
       <c r="BF9" s="10">
-        <v>800</v>
+        <v>1900</v>
       </c>
       <c r="BG9" s="10">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="BH9" s="6" t="s">
         <v>107</v>
@@ -2692,16 +2674,16 @@
         <v>65</v>
       </c>
       <c r="Z10" s="10">
-        <v>284.37</v>
+        <v>590.37</v>
       </c>
       <c r="AA10" s="10">
         <v>0</v>
       </c>
       <c r="AB10" s="10">
-        <v>284.37</v>
+        <v>590.37</v>
       </c>
       <c r="AC10" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD10" s="6" t="s">
         <v>65</v>
@@ -2710,22 +2692,22 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF10" s="7">
-        <v>176690</v>
+        <v>178001</v>
       </c>
       <c r="AG10" s="9">
-        <v>46175.35753472222</v>
+        <v>46190.609131944446</v>
       </c>
       <c r="AH10" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AI10" s="6" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AJ10" s="11">
         <v>0.014939759036144</v>
       </c>
       <c r="AK10" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL10" s="6" t="s">
         <v>110</v>
@@ -2740,7 +2722,7 @@
         <v>65</v>
       </c>
       <c r="AP10" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AQ10" s="10">
         <v>0</v>
@@ -2749,10 +2731,10 @@
         <v>65</v>
       </c>
       <c r="AS10" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AT10" s="7">
-        <v>2655</v>
+        <v>2646</v>
       </c>
       <c r="AU10" s="6" t="s">
         <v>82</v>
@@ -2761,13 +2743,13 @@
         <v>83</v>
       </c>
       <c r="AW10" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AX10" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY10" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ10" s="6" t="s">
         <v>65</v>
@@ -2794,10 +2776,10 @@
         <v>620</v>
       </c>
       <c r="BH10" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BI10" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BJ10" s="6" t="s">
         <v>89</v>
@@ -2811,19 +2793,19 @@
         <v>2019</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>65</v>
@@ -2832,7 +2814,7 @@
         <v>68</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>68</v>
@@ -2841,7 +2823,7 @@
         <v>65</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N11" s="6" t="s">
         <v>65</v>
@@ -2859,10 +2841,10 @@
         <v>65</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U11" s="6" t="s">
         <v>65</v>
@@ -2880,16 +2862,16 @@
         <v>65</v>
       </c>
       <c r="Z11" s="10">
-        <v>1190.42</v>
+        <v>1914.17</v>
       </c>
       <c r="AA11" s="10">
         <v>0</v>
       </c>
       <c r="AB11" s="10">
-        <v>1190.42</v>
+        <v>1914.17</v>
       </c>
       <c r="AC11" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD11" s="6" t="s">
         <v>65</v>
@@ -2898,10 +2880,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF11" s="7">
-        <v>273298</v>
+        <v>274560</v>
       </c>
       <c r="AG11" s="9">
-        <v>46175.357523148145</v>
+        <v>46185.42972222222</v>
       </c>
       <c r="AH11" s="6" t="s">
         <v>65</v>
@@ -2913,10 +2895,10 @@
         <v>0.014823529411764</v>
       </c>
       <c r="AK11" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AL11" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM11" s="6" t="s">
         <v>65</v>
@@ -2928,7 +2910,7 @@
         <v>65</v>
       </c>
       <c r="AP11" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AQ11" s="10">
         <v>0</v>
@@ -2937,10 +2919,10 @@
         <v>65</v>
       </c>
       <c r="AS11" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AT11" s="7">
-        <v>18390</v>
+        <v>17599</v>
       </c>
       <c r="AU11" s="6" t="s">
         <v>82</v>
@@ -2949,13 +2931,13 @@
         <v>83</v>
       </c>
       <c r="AW11" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AX11" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY11" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ11" s="6" t="s">
         <v>65</v>
@@ -2982,10 +2964,10 @@
         <v>630</v>
       </c>
       <c r="BH11" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BI11" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BJ11" s="6" t="s">
         <v>89</v>
@@ -2999,19 +2981,19 @@
         <v>2022</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>65</v>
@@ -3020,7 +3002,7 @@
         <v>68</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>68</v>
@@ -3029,28 +3011,28 @@
         <v>65</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O12" s="7">
-        <v>258527</v>
-      </c>
-      <c r="P12" s="8" t="s">
-        <v>65</v>
+        <v>258533</v>
+      </c>
+      <c r="P12" s="8">
+        <v>36526</v>
       </c>
       <c r="Q12" s="9">
-        <v>46091.541666666664</v>
+        <v>45873.333333333336</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U12" s="6" t="s">
         <v>65</v>
@@ -3068,16 +3050,16 @@
         <v>65</v>
       </c>
       <c r="Z12" s="10">
-        <v>694.95</v>
+        <v>2022.84</v>
       </c>
       <c r="AA12" s="10">
         <v>0</v>
       </c>
       <c r="AB12" s="10">
-        <v>766.78</v>
+        <v>2155.84</v>
       </c>
       <c r="AC12" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD12" s="6" t="s">
         <v>65</v>
@@ -3086,10 +3068,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF12" s="7">
-        <v>88758</v>
+        <v>149570</v>
       </c>
       <c r="AG12" s="9">
-        <v>46175.3575</v>
+        <v>46181.609398148146</v>
       </c>
       <c r="AH12" s="6" t="s">
         <v>65</v>
@@ -3098,13 +3080,13 @@
         <v>78</v>
       </c>
       <c r="AJ12" s="11">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="AK12" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL12" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AM12" s="6" t="s">
         <v>65</v>
@@ -3116,19 +3098,19 @@
         <v>65</v>
       </c>
       <c r="AP12" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="AQ12" s="10">
-        <v>0</v>
+        <v>113</v>
+      </c>
+      <c r="AQ12" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR12" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS12" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AT12" s="7">
-        <v>16640</v>
+        <v>6939</v>
       </c>
       <c r="AU12" s="6" t="s">
         <v>82</v>
@@ -3137,19 +3119,19 @@
         <v>83</v>
       </c>
       <c r="AW12" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AX12" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY12" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ12" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA12" s="8">
-        <v>46223.458333333336</v>
+        <v>46195.458333333336</v>
       </c>
       <c r="BB12" s="9" t="s">
         <v>65</v>
@@ -3157,23 +3139,23 @@
       <c r="BC12" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="BD12" s="10">
-        <v>0</v>
+      <c r="BD12" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BE12" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF12" s="10">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="BG12" s="10">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="BH12" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BI12" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BJ12" s="6" t="s">
         <v>89</v>
@@ -3181,25 +3163,25 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B13" s="7">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>65</v>
@@ -3208,7 +3190,7 @@
         <v>68</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>68</v>
@@ -3217,28 +3199,28 @@
         <v>65</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N13" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O13" s="7">
-        <v>258547</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>65</v>
+        <v>258539</v>
+      </c>
+      <c r="P13" s="8">
+        <v>45475.125</v>
       </c>
       <c r="Q13" s="9">
-        <v>46098.375</v>
+        <v>45873.333333333336</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="U13" s="6" t="s">
         <v>65</v>
@@ -3256,16 +3238,16 @@
         <v>65</v>
       </c>
       <c r="Z13" s="10">
-        <v>390.72</v>
+        <v>1192.07</v>
       </c>
       <c r="AA13" s="10">
         <v>0</v>
       </c>
       <c r="AB13" s="10">
-        <v>390.72</v>
+        <v>1192.07</v>
       </c>
       <c r="AC13" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD13" s="6" t="s">
         <v>65</v>
@@ -3274,25 +3256,25 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF13" s="7">
-        <v>101633</v>
+        <v>188160</v>
       </c>
       <c r="AG13" s="9">
-        <v>46175.357511574075</v>
+        <v>46190.61891203704</v>
       </c>
       <c r="AH13" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AI13" s="6" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AJ13" s="11">
-        <v>0</v>
+        <v>0.013846153846153</v>
       </c>
       <c r="AK13" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL13" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AM13" s="6" t="s">
         <v>65</v>
@@ -3306,8 +3288,8 @@
       <c r="AP13" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="AQ13" s="10" t="s">
-        <v>65</v>
+      <c r="AQ13" s="10">
+        <v>0</v>
       </c>
       <c r="AR13" s="6" t="s">
         <v>65</v>
@@ -3316,7 +3298,7 @@
         <v>148</v>
       </c>
       <c r="AT13" s="7">
-        <v>22826</v>
+        <v>10671</v>
       </c>
       <c r="AU13" s="6" t="s">
         <v>82</v>
@@ -3328,40 +3310,40 @@
         <v>149</v>
       </c>
       <c r="AX13" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY13" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ13" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA13" s="8">
-        <v>46202.99998842592</v>
+        <v>46223.99998842592</v>
       </c>
       <c r="BB13" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="BD13" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE13" s="10">
+        <v>45500</v>
+      </c>
+      <c r="BF13" s="10">
+        <v>630</v>
+      </c>
+      <c r="BG13" s="10">
+        <v>630</v>
+      </c>
+      <c r="BH13" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="BD13" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE13" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BF13" s="10">
-        <v>620</v>
-      </c>
-      <c r="BG13" s="10">
-        <v>620</v>
-      </c>
-      <c r="BH13" s="6" t="s">
-        <v>151</v>
-      </c>
       <c r="BI13" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="BJ13" s="6" t="s">
         <v>89</v>
@@ -3369,25 +3351,25 @@
     </row>
     <row r="14">
       <c r="A14" s="7">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="B14" s="7">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="F14" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>65</v>
@@ -3396,7 +3378,7 @@
         <v>68</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>68</v>
@@ -3405,16 +3387,16 @@
         <v>65</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N14" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O14" s="7">
-        <v>258533</v>
+        <v>258526</v>
       </c>
       <c r="P14" s="8">
-        <v>36526</v>
+        <v>45351</v>
       </c>
       <c r="Q14" s="9">
         <v>45873.333333333336</v>
@@ -3423,10 +3405,10 @@
         <v>65</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="U14" s="6" t="s">
         <v>65</v>
@@ -3444,16 +3426,16 @@
         <v>65</v>
       </c>
       <c r="Z14" s="10">
-        <v>2022.84</v>
+        <v>2430.95</v>
       </c>
       <c r="AA14" s="10">
         <v>0</v>
       </c>
       <c r="AB14" s="10">
-        <v>2155.84</v>
+        <v>2430.95</v>
       </c>
       <c r="AC14" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD14" s="6" t="s">
         <v>65</v>
@@ -3462,10 +3444,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF14" s="7">
-        <v>148702</v>
+        <v>240681</v>
       </c>
       <c r="AG14" s="9">
-        <v>46175.35748842593</v>
+        <v>46181.6094212963</v>
       </c>
       <c r="AH14" s="6" t="s">
         <v>65</v>
@@ -3474,13 +3456,13 @@
         <v>78</v>
       </c>
       <c r="AJ14" s="11">
-        <v>650</v>
+        <v>0.01575</v>
       </c>
       <c r="AK14" s="6" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="AL14" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM14" s="6" t="s">
         <v>65</v>
@@ -3504,7 +3486,7 @@
         <v>158</v>
       </c>
       <c r="AT14" s="7">
-        <v>7214</v>
+        <v>10087</v>
       </c>
       <c r="AU14" s="6" t="s">
         <v>82</v>
@@ -3516,16 +3498,16 @@
         <v>159</v>
       </c>
       <c r="AX14" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY14" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ14" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA14" s="8">
-        <v>46195.458333333336</v>
+        <v>46223.458333333336</v>
       </c>
       <c r="BB14" s="9" t="s">
         <v>65</v>
@@ -3537,13 +3519,13 @@
         <v>65</v>
       </c>
       <c r="BE14" s="10">
-        <v>1</v>
+        <v>40000</v>
       </c>
       <c r="BF14" s="10">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="BG14" s="10">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="BH14" s="6" t="s">
         <v>160</v>
@@ -3641,7 +3623,7 @@
         <v>433.8</v>
       </c>
       <c r="AC15" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD15" s="6" t="s">
         <v>65</v>
@@ -3650,10 +3632,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF15" s="7">
-        <v>129783</v>
+        <v>131418</v>
       </c>
       <c r="AG15" s="9">
-        <v>46175.3575</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH15" s="6" t="s">
         <v>65</v>
@@ -3665,7 +3647,7 @@
         <v>0.014028056112224</v>
       </c>
       <c r="AK15" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL15" s="6" t="s">
         <v>163</v>
@@ -3680,7 +3662,7 @@
         <v>65</v>
       </c>
       <c r="AP15" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AQ15" s="10">
         <v>0</v>
@@ -3689,10 +3671,10 @@
         <v>65</v>
       </c>
       <c r="AS15" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AT15" s="7">
-        <v>-11572</v>
+        <v>-9424</v>
       </c>
       <c r="AU15" s="6" t="s">
         <v>82</v>
@@ -3701,16 +3683,16 @@
         <v>83</v>
       </c>
       <c r="AW15" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AX15" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY15" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ15" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BA15" s="8">
         <v>46202.99998842592</v>
@@ -3734,10 +3716,10 @@
         <v>630</v>
       </c>
       <c r="BH15" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BI15" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BJ15" s="6" t="s">
         <v>89</v>
@@ -3745,25 +3727,25 @@
     </row>
     <row r="16">
       <c r="A16" s="7">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B16" s="7">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>65</v>
@@ -3772,7 +3754,7 @@
         <v>68</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>68</v>
@@ -3781,16 +3763,16 @@
         <v>65</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N16" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O16" s="7">
-        <v>258528</v>
+        <v>258551</v>
       </c>
       <c r="P16" s="8">
-        <v>45729</v>
+        <v>45092.125</v>
       </c>
       <c r="Q16" s="9">
         <v>45873.333333333336</v>
@@ -3799,10 +3781,10 @@
         <v>65</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="U16" s="6" t="s">
         <v>65</v>
@@ -3820,16 +3802,16 @@
         <v>65</v>
       </c>
       <c r="Z16" s="10">
-        <v>299.75</v>
+        <v>441.44</v>
       </c>
       <c r="AA16" s="10">
         <v>0</v>
       </c>
       <c r="AB16" s="10">
-        <v>299.75</v>
+        <v>441.44</v>
       </c>
       <c r="AC16" s="6" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="AD16" s="6" t="s">
         <v>65</v>
@@ -3838,10 +3820,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF16" s="7">
-        <v>121204</v>
+        <v>180280</v>
       </c>
       <c r="AG16" s="9">
-        <v>46175.3575</v>
+        <v>46185.44417824074</v>
       </c>
       <c r="AH16" s="6" t="s">
         <v>65</v>
@@ -3850,13 +3832,13 @@
         <v>78</v>
       </c>
       <c r="AJ16" s="11">
-        <v>0.014605100550499</v>
+        <v>0.013333333333333</v>
       </c>
       <c r="AK16" s="6" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="AL16" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM16" s="6" t="s">
         <v>65</v>
@@ -3868,19 +3850,19 @@
         <v>65</v>
       </c>
       <c r="AP16" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="AQ16" s="10" t="s">
-        <v>65</v>
+        <v>178</v>
+      </c>
+      <c r="AQ16" s="10">
+        <v>0</v>
       </c>
       <c r="AR16" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS16" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AT16" s="7">
-        <v>5274</v>
+        <v>7255</v>
       </c>
       <c r="AU16" s="6" t="s">
         <v>82</v>
@@ -3889,43 +3871,43 @@
         <v>83</v>
       </c>
       <c r="AW16" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AX16" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY16" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ16" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA16" s="8">
-        <v>46181.458333333336</v>
+        <v>46202.99998842592</v>
       </c>
       <c r="BB16" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC16" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD16" s="10" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="BD16" s="10">
+        <v>0</v>
       </c>
       <c r="BE16" s="10">
-        <v>44505</v>
+        <v>45000</v>
       </c>
       <c r="BF16" s="10">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="BG16" s="10">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="BH16" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BI16" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BJ16" s="6" t="s">
         <v>89</v>
@@ -3933,25 +3915,25 @@
     </row>
     <row r="17">
       <c r="A17" s="7">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B17" s="7">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>65</v>
@@ -3960,7 +3942,7 @@
         <v>68</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>68</v>
@@ -3969,28 +3951,28 @@
         <v>65</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N17" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O17" s="7">
-        <v>258551</v>
-      </c>
-      <c r="P17" s="8">
-        <v>45092.125</v>
+        <v>258547</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="Q17" s="9">
-        <v>45873.333333333336</v>
+        <v>46098.375</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="U17" s="6" t="s">
         <v>65</v>
@@ -4008,16 +3990,16 @@
         <v>65</v>
       </c>
       <c r="Z17" s="10">
-        <v>350.48</v>
+        <v>390.72</v>
       </c>
       <c r="AA17" s="10">
         <v>0</v>
       </c>
       <c r="AB17" s="10">
-        <v>350.48</v>
+        <v>390.72</v>
       </c>
       <c r="AC17" s="6" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="AD17" s="6" t="s">
         <v>65</v>
@@ -4026,10 +4008,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF17" s="7">
-        <v>179292</v>
+        <v>102894</v>
       </c>
       <c r="AG17" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH17" s="6" t="s">
         <v>65</v>
@@ -4038,13 +4020,13 @@
         <v>78</v>
       </c>
       <c r="AJ17" s="11">
-        <v>0.013333333333333</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="6" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="AL17" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AM17" s="6" t="s">
         <v>65</v>
@@ -4056,19 +4038,19 @@
         <v>65</v>
       </c>
       <c r="AP17" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="AQ17" s="10">
-        <v>0</v>
+        <v>187</v>
+      </c>
+      <c r="AQ17" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR17" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS17" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AT17" s="7">
-        <v>7535</v>
+        <v>19471</v>
       </c>
       <c r="AU17" s="6" t="s">
         <v>82</v>
@@ -4077,13 +4059,13 @@
         <v>83</v>
       </c>
       <c r="AW17" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AX17" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY17" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ17" s="6" t="s">
         <v>65</v>
@@ -4095,25 +4077,25 @@
         <v>65</v>
       </c>
       <c r="BC17" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD17" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE17" s="10">
-        <v>45000</v>
+        <v>190</v>
+      </c>
+      <c r="BD17" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="BE17" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BF17" s="10">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="BG17" s="10">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="BH17" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="BI17" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="BJ17" s="6" t="s">
         <v>89</v>
@@ -4121,25 +4103,25 @@
     </row>
     <row r="18">
       <c r="A18" s="7">
+        <v>2023</v>
+      </c>
+      <c r="B18" s="7">
         <v>2022</v>
       </c>
-      <c r="B18" s="7">
-        <v>2021</v>
-      </c>
       <c r="C18" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>65</v>
@@ -4148,7 +4130,7 @@
         <v>68</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>68</v>
@@ -4157,16 +4139,16 @@
         <v>65</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O18" s="7">
-        <v>258539</v>
+        <v>258528</v>
       </c>
       <c r="P18" s="8">
-        <v>45475.125</v>
+        <v>45729</v>
       </c>
       <c r="Q18" s="9">
         <v>45873.333333333336</v>
@@ -4175,10 +4157,10 @@
         <v>65</v>
       </c>
       <c r="S18" s="6" t="s">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="U18" s="6" t="s">
         <v>65</v>
@@ -4196,16 +4178,16 @@
         <v>65</v>
       </c>
       <c r="Z18" s="10">
-        <v>1039.98</v>
+        <v>299.75</v>
       </c>
       <c r="AA18" s="10">
         <v>0</v>
       </c>
       <c r="AB18" s="10">
-        <v>1039.98</v>
+        <v>299.75</v>
       </c>
       <c r="AC18" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD18" s="6" t="s">
         <v>65</v>
@@ -4214,10 +4196,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF18" s="7">
-        <v>187088</v>
+        <v>122267</v>
       </c>
       <c r="AG18" s="9">
-        <v>46175.35753472222</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH18" s="6" t="s">
         <v>65</v>
@@ -4226,13 +4208,13 @@
         <v>78</v>
       </c>
       <c r="AJ18" s="11">
-        <v>0.013846153846153</v>
+        <v>0.014605100550499</v>
       </c>
       <c r="AK18" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL18" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AM18" s="6" t="s">
         <v>65</v>
@@ -4244,19 +4226,19 @@
         <v>65</v>
       </c>
       <c r="AP18" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="AQ18" s="10">
-        <v>0</v>
+        <v>157</v>
+      </c>
+      <c r="AQ18" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR18" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS18" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AT18" s="7">
-        <v>11120</v>
+        <v>5112</v>
       </c>
       <c r="AU18" s="6" t="s">
         <v>82</v>
@@ -4265,43 +4247,43 @@
         <v>83</v>
       </c>
       <c r="AW18" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AX18" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY18" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ18" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA18" s="8">
-        <v>46223.99998842592</v>
+        <v>46265.458333333336</v>
       </c>
       <c r="BB18" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC18" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD18" s="10">
-        <v>0</v>
+        <v>190</v>
+      </c>
+      <c r="BD18" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BE18" s="10">
-        <v>45500</v>
+        <v>44505</v>
       </c>
       <c r="BF18" s="10">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="BG18" s="10">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="BH18" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="BI18" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="BJ18" s="6" t="s">
         <v>89</v>
@@ -4309,25 +4291,25 @@
     </row>
     <row r="19">
       <c r="A19" s="7">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="B19" s="7">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>65</v>
@@ -4336,7 +4318,7 @@
         <v>68</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>68</v>
@@ -4345,28 +4327,28 @@
         <v>65</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O19" s="7">
-        <v>258526</v>
-      </c>
-      <c r="P19" s="8">
-        <v>45351</v>
+        <v>258527</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="Q19" s="9">
-        <v>45873.333333333336</v>
+        <v>46091.541666666664</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="U19" s="6" t="s">
         <v>65</v>
@@ -4384,16 +4366,16 @@
         <v>65</v>
       </c>
       <c r="Z19" s="10">
-        <v>2430.95</v>
+        <v>694.95</v>
       </c>
       <c r="AA19" s="10">
         <v>0</v>
       </c>
       <c r="AB19" s="10">
-        <v>2430.95</v>
+        <v>766.78</v>
       </c>
       <c r="AC19" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD19" s="6" t="s">
         <v>65</v>
@@ -4402,10 +4384,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF19" s="7">
-        <v>239800</v>
+        <v>89572</v>
       </c>
       <c r="AG19" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH19" s="6" t="s">
         <v>65</v>
@@ -4414,37 +4396,37 @@
         <v>78</v>
       </c>
       <c r="AJ19" s="11">
-        <v>0.01575</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL19" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="AM19" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN19" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AO19" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP19" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="AL19" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM19" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN19" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO19" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP19" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="AQ19" s="10" t="s">
-        <v>65</v>
+      <c r="AQ19" s="10">
+        <v>0</v>
       </c>
       <c r="AR19" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS19" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AT19" s="7">
-        <v>10525</v>
+        <v>14285</v>
       </c>
       <c r="AU19" s="6" t="s">
         <v>82</v>
@@ -4453,13 +4435,13 @@
         <v>83</v>
       </c>
       <c r="AW19" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AX19" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY19" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ19" s="6" t="s">
         <v>65</v>
@@ -4473,23 +4455,23 @@
       <c r="BC19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="BD19" s="10" t="s">
-        <v>65</v>
+      <c r="BD19" s="10">
+        <v>0</v>
       </c>
       <c r="BE19" s="10">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="BF19" s="10">
         <v>630</v>
       </c>
       <c r="BG19" s="10">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="BH19" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="BI19" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="BJ19" s="6" t="s">
         <v>89</v>
@@ -4503,19 +4485,19 @@
         <v>2018</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>65</v>
@@ -4524,7 +4506,7 @@
         <v>68</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>68</v>
@@ -4533,7 +4515,7 @@
         <v>65</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N20" s="6" t="s">
         <v>65</v>
@@ -4551,10 +4533,10 @@
         <v>65</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="U20" s="6" t="s">
         <v>65</v>
@@ -4575,13 +4557,13 @@
         <v>200.77</v>
       </c>
       <c r="AA20" s="10">
-        <v>1076.7</v>
+        <v>1440.89</v>
       </c>
       <c r="AB20" s="10">
-        <v>1277.47</v>
+        <v>1641.66</v>
       </c>
       <c r="AC20" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD20" s="6" t="s">
         <v>65</v>
@@ -4590,10 +4572,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF20" s="7">
-        <v>238631</v>
+        <v>238627</v>
       </c>
       <c r="AG20" s="9">
-        <v>46164.408171296294</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH20" s="6" t="s">
         <v>65</v>
@@ -4605,10 +4587,10 @@
         <v>0.015897435897435</v>
       </c>
       <c r="AK20" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL20" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM20" s="6" t="s">
         <v>65</v>
@@ -4620,7 +4602,7 @@
         <v>65</v>
       </c>
       <c r="AP20" s="6" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="AQ20" s="10">
         <v>0</v>
@@ -4629,10 +4611,10 @@
         <v>65</v>
       </c>
       <c r="AS20" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AT20" s="7">
-        <v>8380</v>
+        <v>7965</v>
       </c>
       <c r="AU20" s="6" t="s">
         <v>82</v>
@@ -4641,13 +4623,13 @@
         <v>83</v>
       </c>
       <c r="AW20" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AX20" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY20" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ20" s="6" t="s">
         <v>65</v>
@@ -4674,10 +4656,10 @@
         <v>620</v>
       </c>
       <c r="BH20" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="BI20" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="BJ20" s="6" t="s">
         <v>89</v>
@@ -4691,19 +4673,19 @@
         <v>2020</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>65</v>
@@ -4712,7 +4694,7 @@
         <v>68</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>68</v>
@@ -4721,7 +4703,7 @@
         <v>65</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N21" s="6" t="s">
         <v>65</v>
@@ -4739,10 +4721,10 @@
         <v>65</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="T21" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U21" s="6" t="s">
         <v>65</v>
@@ -4769,7 +4751,7 @@
         <v>229.09</v>
       </c>
       <c r="AC21" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD21" s="6" t="s">
         <v>65</v>
@@ -4778,10 +4760,10 @@
         <v>45861.54583333333</v>
       </c>
       <c r="AF21" s="7">
-        <v>153244</v>
+        <v>154569</v>
       </c>
       <c r="AG21" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.6094212963</v>
       </c>
       <c r="AH21" s="6" t="s">
         <v>65</v>
@@ -4793,10 +4775,10 @@
         <v>0.013793103448275</v>
       </c>
       <c r="AK21" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL21" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AM21" s="6" t="s">
         <v>65</v>
@@ -4808,7 +4790,7 @@
         <v>65</v>
       </c>
       <c r="AP21" s="6" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="AQ21" s="10">
         <v>0</v>
@@ -4817,10 +4799,10 @@
         <v>65</v>
       </c>
       <c r="AS21" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AT21" s="7">
-        <v>9903</v>
+        <v>9537</v>
       </c>
       <c r="AU21" s="6" t="s">
         <v>82</v>
@@ -4829,13 +4811,13 @@
         <v>83</v>
       </c>
       <c r="AW21" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AX21" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY21" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ21" s="6" t="s">
         <v>65</v>
@@ -4862,10 +4844,10 @@
         <v>600</v>
       </c>
       <c r="BH21" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="BI21" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="BJ21" s="6" t="s">
         <v>89</v>
@@ -4879,19 +4861,19 @@
         <v>2021</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D22" s="8">
         <v>45854.9691099537</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>65</v>
@@ -4900,7 +4882,7 @@
         <v>68</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>68</v>
@@ -4909,7 +4891,7 @@
         <v>65</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>65</v>
@@ -4927,10 +4909,10 @@
         <v>65</v>
       </c>
       <c r="S22" s="6" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="U22" s="6" t="s">
         <v>65</v>
@@ -4948,16 +4930,16 @@
         <v>65</v>
       </c>
       <c r="Z22" s="10">
-        <v>857.24</v>
+        <v>1200.84</v>
       </c>
       <c r="AA22" s="10">
         <v>0</v>
       </c>
       <c r="AB22" s="10">
-        <v>897.24</v>
+        <v>1240.84</v>
       </c>
       <c r="AC22" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD22" s="6" t="s">
         <v>65</v>
@@ -4966,10 +4948,10 @@
         <v>45861.56458333333</v>
       </c>
       <c r="AF22" s="7">
-        <v>191102</v>
+        <v>191103</v>
       </c>
       <c r="AG22" s="9">
-        <v>46163.392905092594</v>
+        <v>46185.441666666666</v>
       </c>
       <c r="AH22" s="6" t="s">
         <v>65</v>
@@ -4981,10 +4963,10 @@
         <v>0.015272727272727</v>
       </c>
       <c r="AK22" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL22" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AM22" s="6" t="s">
         <v>65</v>
@@ -4996,7 +4978,7 @@
         <v>65</v>
       </c>
       <c r="AP22" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AQ22" s="10">
         <v>0</v>
@@ -5008,7 +4990,7 @@
         <v>230</v>
       </c>
       <c r="AT22" s="7">
-        <v>3545</v>
+        <v>3370</v>
       </c>
       <c r="AU22" s="6" t="s">
         <v>82</v>
@@ -5020,13 +5002,13 @@
         <v>231</v>
       </c>
       <c r="AX22" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY22" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ22" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BA22" s="8">
         <v>46202.99998842592</v>
@@ -5061,10 +5043,10 @@
     </row>
     <row r="23">
       <c r="A23" s="7">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B23" s="7">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>233</v>
@@ -5103,19 +5085,19 @@
         <v>65</v>
       </c>
       <c r="O23" s="7">
-        <v>258549</v>
+        <v>258532</v>
       </c>
       <c r="P23" s="8">
-        <v>45105.125</v>
+        <v>45344.125</v>
       </c>
       <c r="Q23" s="9">
-        <v>45861.393055555556</v>
+        <v>45873.333333333336</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S23" s="6" t="s">
-        <v>105</v>
+        <v>238</v>
       </c>
       <c r="T23" s="6" t="s">
         <v>233</v>
@@ -5136,16 +5118,16 @@
         <v>65</v>
       </c>
       <c r="Z23" s="10">
-        <v>2040.16</v>
+        <v>381.44</v>
       </c>
       <c r="AA23" s="10">
-        <v>400</v>
+        <v>711.56</v>
       </c>
       <c r="AB23" s="10">
-        <v>2440.16</v>
+        <v>1093</v>
       </c>
       <c r="AC23" s="6" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="AD23" s="6" t="s">
         <v>65</v>
@@ -5154,22 +5136,22 @@
         <v>45873.458333333336</v>
       </c>
       <c r="AF23" s="7">
-        <v>292424</v>
+        <v>287560</v>
       </c>
       <c r="AG23" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH23" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AI23" s="6" t="s">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AJ23" s="11">
-        <v>0.014545454545454</v>
+        <v>0.016190476190476</v>
       </c>
       <c r="AK23" s="6" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="AL23" s="6" t="s">
         <v>235</v>
@@ -5184,19 +5166,19 @@
         <v>65</v>
       </c>
       <c r="AP23" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR23" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS23" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="AQ23" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR23" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS23" s="6" t="s">
-        <v>240</v>
-      </c>
       <c r="AT23" s="7">
-        <v>20785</v>
+        <v>0</v>
       </c>
       <c r="AU23" s="6" t="s">
         <v>82</v>
@@ -5205,19 +5187,19 @@
         <v>83</v>
       </c>
       <c r="AW23" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AX23" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY23" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ23" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA23" s="8">
-        <v>46223.99998842592</v>
+        <v>46188.99998842592</v>
       </c>
       <c r="BB23" s="9" t="s">
         <v>65</v>
@@ -5229,19 +5211,19 @@
         <v>0</v>
       </c>
       <c r="BE23" s="10">
-        <v>41250</v>
+        <v>42000</v>
       </c>
       <c r="BF23" s="10">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="BG23" s="10">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="BH23" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BI23" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BJ23" s="6" t="s">
         <v>89</v>
@@ -5249,25 +5231,25 @@
     </row>
     <row r="24">
       <c r="A24" s="7">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B24" s="7">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="D24" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="F24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>244</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>245</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>65</v>
@@ -5276,7 +5258,7 @@
         <v>68</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>68</v>
@@ -5285,28 +5267,28 @@
         <v>65</v>
       </c>
       <c r="M24" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O24" s="7">
+        <v>258549</v>
+      </c>
+      <c r="P24" s="8">
+        <v>45105.125</v>
+      </c>
+      <c r="Q24" s="9">
+        <v>45861.393055555556</v>
+      </c>
+      <c r="R24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S24" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="N24" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O24" s="7">
-        <v>258532</v>
-      </c>
-      <c r="P24" s="8">
-        <v>45344.125</v>
-      </c>
-      <c r="Q24" s="9">
-        <v>45873.333333333336</v>
-      </c>
-      <c r="R24" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S24" s="6" t="s">
-        <v>229</v>
-      </c>
       <c r="T24" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U24" s="6" t="s">
         <v>65</v>
@@ -5324,16 +5306,16 @@
         <v>65</v>
       </c>
       <c r="Z24" s="10">
-        <v>381.44</v>
+        <v>2285.04</v>
       </c>
       <c r="AA24" s="10">
-        <v>711.56</v>
+        <v>400</v>
       </c>
       <c r="AB24" s="10">
-        <v>1093</v>
+        <v>2685.04</v>
       </c>
       <c r="AC24" s="6" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="AD24" s="6" t="s">
         <v>65</v>
@@ -5342,10 +5324,10 @@
         <v>45873.458333333336</v>
       </c>
       <c r="AF24" s="7">
-        <v>286674</v>
+        <v>293844</v>
       </c>
       <c r="AG24" s="9">
-        <v>46175.357511574075</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH24" s="6" t="s">
         <v>65</v>
@@ -5354,13 +5336,13 @@
         <v>78</v>
       </c>
       <c r="AJ24" s="11">
-        <v>0.016190476190476</v>
+        <v>0.014545454545454</v>
       </c>
       <c r="AK24" s="6" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="AL24" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AM24" s="6" t="s">
         <v>65</v>
@@ -5372,7 +5354,7 @@
         <v>65</v>
       </c>
       <c r="AP24" s="6" t="s">
-        <v>157</v>
+        <v>248</v>
       </c>
       <c r="AQ24" s="10">
         <v>0</v>
@@ -5381,10 +5363,10 @@
         <v>65</v>
       </c>
       <c r="AS24" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AT24" s="7">
-        <v>0</v>
+        <v>19923</v>
       </c>
       <c r="AU24" s="6" t="s">
         <v>82</v>
@@ -5393,19 +5375,19 @@
         <v>83</v>
       </c>
       <c r="AW24" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AX24" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY24" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ24" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA24" s="8">
-        <v>46188.99998842592</v>
+        <v>46223.99998842592</v>
       </c>
       <c r="BB24" s="9" t="s">
         <v>65</v>
@@ -5417,19 +5399,19 @@
         <v>0</v>
       </c>
       <c r="BE24" s="10">
-        <v>42000</v>
+        <v>41250</v>
       </c>
       <c r="BF24" s="10">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="BG24" s="10">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="BH24" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="BI24" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="BJ24" s="6" t="s">
         <v>89</v>
@@ -5443,37 +5425,37 @@
         <v>2022</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D25" s="8">
         <v>45911.83042086806</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J25" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="K25" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="K25" s="6" t="s">
-        <v>254</v>
-      </c>
       <c r="L25" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>65</v>
@@ -5491,10 +5473,10 @@
         <v>65</v>
       </c>
       <c r="S25" s="6" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="T25" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="U25" s="6" t="s">
         <v>65</v>
@@ -5521,7 +5503,7 @@
         <v>479.38</v>
       </c>
       <c r="AC25" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD25" s="6" t="s">
         <v>65</v>
@@ -5530,10 +5512,10 @@
         <v>45911.791666666664</v>
       </c>
       <c r="AF25" s="7">
-        <v>128962</v>
+        <v>130237</v>
       </c>
       <c r="AG25" s="9">
-        <v>46175.35753472222</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH25" s="6" t="s">
         <v>65</v>
@@ -5545,10 +5527,10 @@
         <v>0.013737373737373</v>
       </c>
       <c r="AK25" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL25" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM25" s="6" t="s">
         <v>65</v>
@@ -5560,7 +5542,7 @@
         <v>65</v>
       </c>
       <c r="AP25" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ25" s="10">
         <v>0</v>
@@ -5569,10 +5551,10 @@
         <v>65</v>
       </c>
       <c r="AS25" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AT25" s="7">
-        <v>6019</v>
+        <v>5596</v>
       </c>
       <c r="AU25" s="6" t="s">
         <v>82</v>
@@ -5581,19 +5563,19 @@
         <v>83</v>
       </c>
       <c r="AW25" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AX25" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY25" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ25" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA25" s="8">
-        <v>46181.48611111111</v>
+        <v>46230.48611111111</v>
       </c>
       <c r="BB25" s="9" t="s">
         <v>65</v>
@@ -5614,10 +5596,10 @@
         <v>680</v>
       </c>
       <c r="BH25" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BI25" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BJ25" s="6" t="s">
         <v>89</v>
@@ -5631,37 +5613,37 @@
         <v>2022</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D26" s="8">
         <v>45916.71897465278</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>65</v>
@@ -5679,10 +5661,10 @@
         <v>65</v>
       </c>
       <c r="S26" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="U26" s="6" t="s">
         <v>65</v>
@@ -5709,7 +5691,7 @@
         <v>670.08</v>
       </c>
       <c r="AC26" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD26" s="6" t="s">
         <v>65</v>
@@ -5718,10 +5700,10 @@
         <v>45915.458333333336</v>
       </c>
       <c r="AF26" s="7">
-        <v>117956</v>
+        <v>118475</v>
       </c>
       <c r="AG26" s="9">
-        <v>46175.3575</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH26" s="6" t="s">
         <v>65</v>
@@ -5733,10 +5715,10 @@
         <v>0.013765182186234</v>
       </c>
       <c r="AK26" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL26" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM26" s="6" t="s">
         <v>65</v>
@@ -5748,7 +5730,7 @@
         <v>65</v>
       </c>
       <c r="AP26" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ26" s="10">
         <v>0</v>
@@ -5757,10 +5739,10 @@
         <v>65</v>
       </c>
       <c r="AS26" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AT26" s="7">
-        <v>3886</v>
+        <v>3716</v>
       </c>
       <c r="AU26" s="6" t="s">
         <v>82</v>
@@ -5769,19 +5751,19 @@
         <v>83</v>
       </c>
       <c r="AW26" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AX26" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY26" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ26" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA26" s="8">
-        <v>46181.99998842592</v>
+        <v>46230.99998842592</v>
       </c>
       <c r="BB26" s="9" t="s">
         <v>65</v>
@@ -5802,10 +5784,10 @@
         <v>680</v>
       </c>
       <c r="BH26" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="BI26" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="BJ26" s="6" t="s">
         <v>89</v>
@@ -5819,37 +5801,37 @@
         <v>2022</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D27" s="8">
         <v>45951.78161053241</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N27" s="6" t="s">
         <v>65</v>
@@ -5867,10 +5849,10 @@
         <v>65</v>
       </c>
       <c r="S27" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U27" s="6" t="s">
         <v>65</v>
@@ -5897,7 +5879,7 @@
         <v>595.14</v>
       </c>
       <c r="AC27" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD27" s="6" t="s">
         <v>65</v>
@@ -5906,10 +5888,10 @@
         <v>45957.458333333336</v>
       </c>
       <c r="AF27" s="7">
-        <v>129846</v>
+        <v>130867</v>
       </c>
       <c r="AG27" s="9">
-        <v>46175.3575</v>
+        <v>46181.609398148146</v>
       </c>
       <c r="AH27" s="6" t="s">
         <v>65</v>
@@ -5921,10 +5903,10 @@
         <v>0.013765182186234</v>
       </c>
       <c r="AK27" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL27" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM27" s="6" t="s">
         <v>65</v>
@@ -5936,7 +5918,7 @@
         <v>65</v>
       </c>
       <c r="AP27" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ27" s="10">
         <v>0</v>
@@ -5945,10 +5927,10 @@
         <v>65</v>
       </c>
       <c r="AS27" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AT27" s="7">
-        <v>5371</v>
+        <v>5140</v>
       </c>
       <c r="AU27" s="6" t="s">
         <v>82</v>
@@ -5957,19 +5939,19 @@
         <v>83</v>
       </c>
       <c r="AW27" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AX27" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY27" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ27" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA27" s="8">
-        <v>46181.99998842592</v>
+        <v>46230.99998842592</v>
       </c>
       <c r="BB27" s="9" t="s">
         <v>65</v>
@@ -5990,10 +5972,10 @@
         <v>680</v>
       </c>
       <c r="BH27" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="BI27" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="BJ27" s="6" t="s">
         <v>89</v>
@@ -6007,37 +5989,37 @@
         <v>2020</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D28" s="8">
         <v>45959.49119818287</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>65</v>
@@ -6055,10 +6037,10 @@
         <v>65</v>
       </c>
       <c r="S28" s="6" t="s">
-        <v>229</v>
+        <v>113</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="U28" s="6" t="s">
         <v>65</v>
@@ -6076,16 +6058,16 @@
         <v>65</v>
       </c>
       <c r="Z28" s="10">
-        <v>832.5</v>
+        <v>1340.58</v>
       </c>
       <c r="AA28" s="10">
         <v>0</v>
       </c>
       <c r="AB28" s="10">
-        <v>832.5</v>
+        <v>1340.58</v>
       </c>
       <c r="AC28" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD28" s="6" t="s">
         <v>65</v>
@@ -6094,25 +6076,25 @@
         <v>45958.791666666664</v>
       </c>
       <c r="AF28" s="7">
-        <v>211265</v>
+        <v>212100</v>
       </c>
       <c r="AG28" s="9">
-        <v>46175.357511574075</v>
+        <v>46190.628958333335</v>
       </c>
       <c r="AH28" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AI28" s="6" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AJ28" s="11">
         <v>0.015089820359281</v>
       </c>
       <c r="AK28" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL28" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AM28" s="6" t="s">
         <v>65</v>
@@ -6124,7 +6106,7 @@
         <v>65</v>
       </c>
       <c r="AP28" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ28" s="10">
         <v>0</v>
@@ -6133,10 +6115,10 @@
         <v>65</v>
       </c>
       <c r="AS28" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AT28" s="7">
-        <v>4878</v>
+        <v>4656</v>
       </c>
       <c r="AU28" s="6" t="s">
         <v>82</v>
@@ -6145,13 +6127,13 @@
         <v>83</v>
       </c>
       <c r="AW28" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AX28" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ28" s="6" t="s">
         <v>65</v>
@@ -6178,10 +6160,10 @@
         <v>630</v>
       </c>
       <c r="BH28" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="BI28" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="BJ28" s="6" t="s">
         <v>89</v>
@@ -6195,37 +6177,37 @@
         <v>2022</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D29" s="8">
         <v>45986.703306284726</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>65</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>65</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>65</v>
@@ -6243,10 +6225,10 @@
         <v>65</v>
       </c>
       <c r="S29" s="6" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="U29" s="6" t="s">
         <v>65</v>
@@ -6273,7 +6255,7 @@
         <v>800.63</v>
       </c>
       <c r="AC29" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD29" s="6" t="s">
         <v>65</v>
@@ -6282,10 +6264,10 @@
         <v>45980.666666666664</v>
       </c>
       <c r="AF29" s="7">
-        <v>127507</v>
+        <v>127892</v>
       </c>
       <c r="AG29" s="9">
-        <v>46175.3575</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH29" s="6" t="s">
         <v>65</v>
@@ -6297,10 +6279,10 @@
         <v>0.014639397201291</v>
       </c>
       <c r="AK29" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL29" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM29" s="6" t="s">
         <v>65</v>
@@ -6312,7 +6294,7 @@
         <v>65</v>
       </c>
       <c r="AP29" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ29" s="10" t="s">
         <v>65</v>
@@ -6321,10 +6303,10 @@
         <v>65</v>
       </c>
       <c r="AS29" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AT29" s="7">
-        <v>2913</v>
+        <v>2747</v>
       </c>
       <c r="AU29" s="6" t="s">
         <v>82</v>
@@ -6333,13 +6315,13 @@
         <v>83</v>
       </c>
       <c r="AW29" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AX29" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY29" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ29" s="6" t="s">
         <v>65</v>
@@ -6366,10 +6348,10 @@
         <v>700</v>
       </c>
       <c r="BH29" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BI29" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="BJ29" s="6" t="s">
         <v>89</v>
@@ -6383,37 +6365,37 @@
         <v>2022</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D30" s="8">
         <v>45988.58394895833</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H30" s="7">
         <v>25</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>70</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>65</v>
@@ -6431,10 +6413,10 @@
         <v>65</v>
       </c>
       <c r="S30" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="T30" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="U30" s="6" t="s">
         <v>65</v>
@@ -6461,7 +6443,7 @@
         <v>0</v>
       </c>
       <c r="AC30" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD30" s="6" t="s">
         <v>65</v>
@@ -6470,10 +6452,10 @@
         <v>45986.458333333336</v>
       </c>
       <c r="AF30" s="7">
-        <v>103022</v>
+        <v>103115</v>
       </c>
       <c r="AG30" s="9">
-        <v>46175.35753472222</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH30" s="6" t="s">
         <v>65</v>
@@ -6485,10 +6467,10 @@
         <v>0.050560747663551</v>
       </c>
       <c r="AK30" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL30" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM30" s="6" t="s">
         <v>65</v>
@@ -6500,7 +6482,7 @@
         <v>65</v>
       </c>
       <c r="AP30" s="6" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="AQ30" s="10">
         <v>0</v>
@@ -6512,7 +6494,7 @@
         <v>301</v>
       </c>
       <c r="AT30" s="7">
-        <v>3735</v>
+        <v>3459</v>
       </c>
       <c r="AU30" s="6" t="s">
         <v>82</v>
@@ -6524,13 +6506,13 @@
         <v>65</v>
       </c>
       <c r="AX30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY30" s="6" t="s">
         <v>302</v>
       </c>
       <c r="AZ30" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BA30" s="8">
         <v>46198.53125</v>
@@ -6539,7 +6521,7 @@
         <v>65</v>
       </c>
       <c r="BC30" s="6" t="s">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="BD30" s="10">
         <v>0</v>
@@ -6589,13 +6571,13 @@
         <v>65</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>307</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>65</v>
@@ -6649,7 +6631,7 @@
         <v>400.54</v>
       </c>
       <c r="AC31" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD31" s="6" t="s">
         <v>65</v>
@@ -6658,10 +6640,10 @@
         <v>46031.791666666664</v>
       </c>
       <c r="AF31" s="7">
-        <v>106081</v>
+        <v>106378</v>
       </c>
       <c r="AG31" s="9">
-        <v>46175.3575</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH31" s="6" t="s">
         <v>65</v>
@@ -6673,7 +6655,7 @@
         <v>0.013255360623781</v>
       </c>
       <c r="AK31" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL31" s="6" t="s">
         <v>306</v>
@@ -6688,7 +6670,7 @@
         <v>65</v>
       </c>
       <c r="AP31" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ31" s="10" t="s">
         <v>65</v>
@@ -6700,7 +6682,7 @@
         <v>310</v>
       </c>
       <c r="AT31" s="7">
-        <v>1519</v>
+        <v>1424</v>
       </c>
       <c r="AU31" s="6" t="s">
         <v>82</v>
@@ -6712,10 +6694,10 @@
         <v>311</v>
       </c>
       <c r="AX31" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY31" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ31" s="6" t="s">
         <v>65</v>
@@ -6727,7 +6709,7 @@
         <v>65</v>
       </c>
       <c r="BC31" s="6" t="s">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="BD31" s="10" t="s">
         <v>65</v>
@@ -6777,13 +6759,13 @@
         <v>65</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>315</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>70</v>
@@ -6837,7 +6819,7 @@
         <v>112.22</v>
       </c>
       <c r="AC32" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD32" s="6" t="s">
         <v>65</v>
@@ -6846,10 +6828,10 @@
         <v>46041.458333333336</v>
       </c>
       <c r="AF32" s="7">
-        <v>225001</v>
+        <v>225286</v>
       </c>
       <c r="AG32" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH32" s="6" t="s">
         <v>65</v>
@@ -6861,7 +6843,7 @@
         <v>0.05090909090909</v>
       </c>
       <c r="AK32" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL32" s="6" t="s">
         <v>65</v>
@@ -6876,7 +6858,7 @@
         <v>65</v>
       </c>
       <c r="AP32" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ32" s="10">
         <v>0</v>
@@ -6888,7 +6870,7 @@
         <v>319</v>
       </c>
       <c r="AT32" s="7">
-        <v>2920</v>
+        <v>2582</v>
       </c>
       <c r="AU32" s="6" t="s">
         <v>82</v>
@@ -6965,13 +6947,13 @@
         <v>65</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>325</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L33" s="6" t="s">
         <v>65</v>
@@ -7025,7 +7007,7 @@
         <v>143.59</v>
       </c>
       <c r="AC33" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD33" s="6" t="s">
         <v>65</v>
@@ -7034,10 +7016,10 @@
         <v>46087.625</v>
       </c>
       <c r="AF33" s="7">
-        <v>82643</v>
+        <v>83668</v>
       </c>
       <c r="AG33" s="9">
-        <v>46175.3575</v>
+        <v>46181.609398148146</v>
       </c>
       <c r="AH33" s="6" t="s">
         <v>65</v>
@@ -7049,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL33" s="6" t="s">
         <v>324</v>
@@ -7064,7 +7046,7 @@
         <v>65</v>
       </c>
       <c r="AP33" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ33" s="10" t="s">
         <v>65</v>
@@ -7076,7 +7058,7 @@
         <v>328</v>
       </c>
       <c r="AT33" s="7">
-        <v>8678</v>
+        <v>7685</v>
       </c>
       <c r="AU33" s="6" t="s">
         <v>82</v>
@@ -7088,10 +7070,10 @@
         <v>329</v>
       </c>
       <c r="AX33" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY33" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ33" s="6" t="s">
         <v>65</v>
@@ -7153,13 +7135,13 @@
         <v>65</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>334</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>65</v>
@@ -7183,7 +7165,7 @@
         <v>65</v>
       </c>
       <c r="S34" s="6" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="T34" s="6" t="s">
         <v>331</v>
@@ -7204,16 +7186,16 @@
         <v>65</v>
       </c>
       <c r="Z34" s="10">
-        <v>294.79</v>
+        <v>802.87</v>
       </c>
       <c r="AA34" s="10">
         <v>0</v>
       </c>
       <c r="AB34" s="10">
-        <v>294.79</v>
+        <v>802.87</v>
       </c>
       <c r="AC34" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD34" s="6" t="s">
         <v>65</v>
@@ -7222,10 +7204,10 @@
         <v>46092.708333333336</v>
       </c>
       <c r="AF34" s="7">
-        <v>155332</v>
+        <v>156083</v>
       </c>
       <c r="AG34" s="9">
-        <v>46175.357511574075</v>
+        <v>46185.4762962963</v>
       </c>
       <c r="AH34" s="6" t="s">
         <v>65</v>
@@ -7237,7 +7219,7 @@
         <v>0.015831660251596</v>
       </c>
       <c r="AK34" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL34" s="6" t="s">
         <v>333</v>
@@ -7252,7 +7234,7 @@
         <v>65</v>
       </c>
       <c r="AP34" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ34" s="10">
         <v>0</v>
@@ -7264,7 +7246,7 @@
         <v>336</v>
       </c>
       <c r="AT34" s="7">
-        <v>-10230</v>
+        <v>-8430</v>
       </c>
       <c r="AU34" s="6" t="s">
         <v>82</v>
@@ -7276,10 +7258,10 @@
         <v>337</v>
       </c>
       <c r="AX34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ34" s="6" t="s">
         <v>65</v>
@@ -7401,7 +7383,7 @@
         <v>194.95</v>
       </c>
       <c r="AC35" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD35" s="6" t="s">
         <v>65</v>
@@ -7440,7 +7422,7 @@
         <v>65</v>
       </c>
       <c r="AP35" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ35" s="10" t="s">
         <v>65</v>
@@ -7464,16 +7446,16 @@
         <v>65</v>
       </c>
       <c r="AX35" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY35" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ35" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA35" s="8">
-        <v>46181.458333333336</v>
+        <v>46230.458333333336</v>
       </c>
       <c r="BB35" s="9" t="s">
         <v>65</v>
@@ -7488,7 +7470,7 @@
         <v>65</v>
       </c>
       <c r="BF35" s="10">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="BG35" s="10">
         <v>700</v>
@@ -7529,13 +7511,13 @@
         <v>65</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>352</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>65</v>
@@ -7589,7 +7571,7 @@
         <v>581.49</v>
       </c>
       <c r="AC36" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD36" s="6" t="s">
         <v>65</v>
@@ -7598,10 +7580,10 @@
         <v>46097.805555555555</v>
       </c>
       <c r="AF36" s="7">
-        <v>102507</v>
+        <v>103578</v>
       </c>
       <c r="AG36" s="9">
-        <v>46175.35748842593</v>
+        <v>46181.609398148146</v>
       </c>
       <c r="AH36" s="6" t="s">
         <v>65</v>
@@ -7613,7 +7595,7 @@
         <v>0.013207547169811</v>
       </c>
       <c r="AK36" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL36" s="6" t="s">
         <v>351</v>
@@ -7628,7 +7610,7 @@
         <v>65</v>
       </c>
       <c r="AP36" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ36" s="10">
         <v>0</v>
@@ -7640,7 +7622,7 @@
         <v>355</v>
       </c>
       <c r="AT36" s="7">
-        <v>4367</v>
+        <v>3973</v>
       </c>
       <c r="AU36" s="6" t="s">
         <v>82</v>
@@ -7652,22 +7634,22 @@
         <v>65</v>
       </c>
       <c r="AX36" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY36" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ36" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA36" s="8">
-        <v>46181.99998842592</v>
+        <v>46265.99998842592</v>
       </c>
       <c r="BB36" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC36" s="6" t="s">
-        <v>356</v>
+        <v>190</v>
       </c>
       <c r="BD36" s="10">
         <v>0</v>
@@ -7682,10 +7664,10 @@
         <v>700</v>
       </c>
       <c r="BH36" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BI36" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BJ36" s="6" t="s">
         <v>89</v>
@@ -7699,37 +7681,37 @@
         <v>2019</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D37" s="8">
         <v>46119.56219482639</v>
       </c>
       <c r="E37" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G37" s="6" t="s">
+      <c r="H37" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="J37" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="H37" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J37" s="6" t="s">
+      <c r="K37" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M37" s="6" t="s">
         <v>361</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M37" s="6" t="s">
-        <v>362</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>65</v>
@@ -7747,10 +7729,10 @@
         <v>65</v>
       </c>
       <c r="S37" s="6" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="T37" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="U37" s="6" t="s">
         <v>65</v>
@@ -7777,7 +7759,7 @@
         <v>832.11</v>
       </c>
       <c r="AC37" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD37" s="6" t="s">
         <v>65</v>
@@ -7786,10 +7768,10 @@
         <v>46118.850694444445</v>
       </c>
       <c r="AF37" s="7">
-        <v>185000</v>
+        <v>184905</v>
       </c>
       <c r="AG37" s="9">
-        <v>46176.39858796296</v>
+        <v>46181.6094212963</v>
       </c>
       <c r="AH37" s="6" t="s">
         <v>65</v>
@@ -7801,10 +7783,10 @@
         <v>0.015764705882352</v>
       </c>
       <c r="AK37" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AL37" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AM37" s="6" t="s">
         <v>65</v>
@@ -7816,7 +7798,7 @@
         <v>65</v>
       </c>
       <c r="AP37" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ37" s="10">
         <v>0</v>
@@ -7825,10 +7807,10 @@
         <v>65</v>
       </c>
       <c r="AS37" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AT37" s="7">
-        <v>2038</v>
+        <v>1573</v>
       </c>
       <c r="AU37" s="6" t="s">
         <v>82</v>
@@ -7840,10 +7822,10 @@
         <v>65</v>
       </c>
       <c r="AX37" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY37" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ37" s="6" t="s">
         <v>65</v>
@@ -7870,10 +7852,10 @@
         <v>670</v>
       </c>
       <c r="BH37" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="BI37" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="BJ37" s="6" t="s">
         <v>89</v>
@@ -7893,31 +7875,31 @@
         <v>46135.522659375</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="J38" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="H38" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>367</v>
-      </c>
       <c r="K38" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L38" s="6" t="s">
         <v>70</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>65</v>
@@ -7935,10 +7917,10 @@
         <v>65</v>
       </c>
       <c r="S38" s="6" t="s">
-        <v>354</v>
+        <v>126</v>
       </c>
       <c r="T38" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U38" s="6" t="s">
         <v>65</v>
@@ -7956,16 +7938,16 @@
         <v>65</v>
       </c>
       <c r="Z38" s="10">
-        <v>90.96</v>
+        <v>131.9</v>
       </c>
       <c r="AA38" s="10">
         <v>0</v>
       </c>
       <c r="AB38" s="10">
-        <v>90.96</v>
+        <v>131.9</v>
       </c>
       <c r="AC38" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD38" s="6" t="s">
         <v>65</v>
@@ -7974,10 +7956,10 @@
         <v>46119.708333333336</v>
       </c>
       <c r="AF38" s="7">
-        <v>248739</v>
+        <v>249059</v>
       </c>
       <c r="AG38" s="9">
-        <v>46175.357511574075</v>
+        <v>46185.43822916667</v>
       </c>
       <c r="AH38" s="6" t="s">
         <v>65</v>
@@ -7989,7 +7971,7 @@
         <v>0.053635736725155</v>
       </c>
       <c r="AK38" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL38" s="6" t="s">
         <v>65</v>
@@ -8004,7 +7986,7 @@
         <v>65</v>
       </c>
       <c r="AP38" s="6" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="AQ38" s="10">
         <v>0</v>
@@ -8013,10 +7995,10 @@
         <v>65</v>
       </c>
       <c r="AS38" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AT38" s="7">
-        <v>383</v>
+        <v>429</v>
       </c>
       <c r="AU38" s="6" t="s">
         <v>82</v>
@@ -8058,10 +8040,10 @@
         <v>2100</v>
       </c>
       <c r="BH38" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="BI38" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="BJ38" s="6" t="s">
         <v>89</v>
@@ -8075,37 +8057,37 @@
         <v>2021</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D39" s="8">
         <v>46127.52819641204</v>
       </c>
       <c r="E39" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G39" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="F39" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G39" s="6" t="s">
+      <c r="H39" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="J39" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="H39" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J39" s="6" t="s">
+      <c r="K39" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39" s="6" t="s">
         <v>375</v>
-      </c>
-      <c r="K39" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M39" s="6" t="s">
-        <v>376</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>65</v>
@@ -8123,10 +8105,10 @@
         <v>65</v>
       </c>
       <c r="S39" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="T39" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="U39" s="6" t="s">
         <v>65</v>
@@ -8153,7 +8135,7 @@
         <v>150.96</v>
       </c>
       <c r="AC39" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD39" s="6" t="s">
         <v>65</v>
@@ -8162,10 +8144,10 @@
         <v>46125.458333333336</v>
       </c>
       <c r="AF39" s="7">
-        <v>200440</v>
+        <v>201539</v>
       </c>
       <c r="AG39" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.60943287037</v>
       </c>
       <c r="AH39" s="6" t="s">
         <v>65</v>
@@ -8177,10 +8159,10 @@
         <v>0.0208</v>
       </c>
       <c r="AK39" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL39" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AM39" s="6" t="s">
         <v>65</v>
@@ -8192,7 +8174,7 @@
         <v>65</v>
       </c>
       <c r="AP39" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ39" s="10">
         <v>0</v>
@@ -8201,10 +8183,10 @@
         <v>65</v>
       </c>
       <c r="AS39" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AT39" s="7">
-        <v>4010</v>
+        <v>3564</v>
       </c>
       <c r="AU39" s="6" t="s">
         <v>82</v>
@@ -8216,10 +8198,10 @@
         <v>65</v>
       </c>
       <c r="AX39" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY39" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ39" s="6" t="s">
         <v>65</v>
@@ -8246,10 +8228,10 @@
         <v>650</v>
       </c>
       <c r="BH39" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="BI39" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="BJ39" s="6" t="s">
         <v>89</v>
@@ -8263,19 +8245,19 @@
         <v>2026</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D40" s="8">
         <v>46148.59058966435</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>380</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>381</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>65</v>
@@ -8284,7 +8266,7 @@
         <v>342</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>342</v>
@@ -8293,7 +8275,7 @@
         <v>65</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>65</v>
@@ -8311,10 +8293,10 @@
         <v>65</v>
       </c>
       <c r="S40" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="T40" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="U40" s="6" t="s">
         <v>65</v>
@@ -8338,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AB40" s="10">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AC40" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD40" s="6" t="s">
         <v>65</v>
@@ -8365,31 +8347,31 @@
         <v>0</v>
       </c>
       <c r="AK40" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="AL40" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AO40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP40" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="AQ40" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="AR40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS40" s="6" t="s">
         <v>385</v>
-      </c>
-      <c r="AL40" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="AM40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP40" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="AQ40" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="AR40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS40" s="6" t="s">
-        <v>386</v>
       </c>
       <c r="AT40" s="7">
         <v>0</v>
@@ -8404,10 +8386,10 @@
         <v>65</v>
       </c>
       <c r="AX40" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY40" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ40" s="6" t="s">
         <v>65</v>
@@ -8419,7 +8401,7 @@
         <v>65</v>
       </c>
       <c r="BC40" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BD40" s="10" t="s">
         <v>65</v>
@@ -8434,10 +8416,10 @@
         <v>1200</v>
       </c>
       <c r="BH40" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BI40" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BJ40" s="6" t="s">
         <v>89</v>
@@ -8451,37 +8433,37 @@
         <v>2019</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D41" s="8">
         <v>45889.59072010417</v>
       </c>
       <c r="E41" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="F41" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G41" s="6" t="s">
+      <c r="H41" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="J41" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="H41" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J41" s="6" t="s">
+      <c r="K41" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M41" s="6" t="s">
         <v>392</v>
-      </c>
-      <c r="K41" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="L41" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M41" s="6" t="s">
-        <v>393</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>65</v>
@@ -8502,7 +8484,7 @@
         <v>166</v>
       </c>
       <c r="T41" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="U41" s="6" t="s">
         <v>65</v>
@@ -8529,7 +8511,7 @@
         <v>944.54</v>
       </c>
       <c r="AC41" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD41" s="6" t="s">
         <v>65</v>
@@ -8538,10 +8520,10 @@
         <v>46146.458333333336</v>
       </c>
       <c r="AF41" s="7">
-        <v>224499</v>
+        <v>225813</v>
       </c>
       <c r="AG41" s="9">
-        <v>46175.357523148145</v>
+        <v>46181.6094212963</v>
       </c>
       <c r="AH41" s="6" t="s">
         <v>65</v>
@@ -8553,10 +8535,10 @@
         <v>0.014</v>
       </c>
       <c r="AK41" s="6" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL41" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AM41" s="6" t="s">
         <v>65</v>
@@ -8568,7 +8550,7 @@
         <v>65</v>
       </c>
       <c r="AP41" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AQ41" s="10" t="s">
         <v>65</v>
@@ -8577,10 +8559,10 @@
         <v>65</v>
       </c>
       <c r="AS41" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AT41" s="7">
-        <v>3293</v>
+        <v>3028</v>
       </c>
       <c r="AU41" s="6" t="s">
         <v>82</v>
@@ -8589,13 +8571,13 @@
         <v>83</v>
       </c>
       <c r="AW41" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AX41" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY41" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ41" s="6" t="s">
         <v>65</v>
@@ -8622,10 +8604,10 @@
         <v>630</v>
       </c>
       <c r="BH41" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="BI41" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="BJ41" s="6" t="s">
         <v>89</v>
@@ -8633,64 +8615,64 @@
     </row>
     <row r="42">
       <c r="A42" s="7">
-        <v>2027</v>
+        <v>2018</v>
       </c>
       <c r="B42" s="7">
-        <v>2026</v>
+        <v>2017</v>
       </c>
       <c r="C42" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="D42" s="8">
+        <v>46153.58720679398</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="D42" s="8">
-        <v>46148.57752453704</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="J42" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="H42" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="J42" s="6" t="s">
+      <c r="K42" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M42" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="K42" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M42" s="6" t="s">
+      <c r="N42" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O42" s="7">
+        <v>346470</v>
+      </c>
+      <c r="P42" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q42" s="9">
+        <v>46150.583333333336</v>
+      </c>
+      <c r="R42" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S42" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="N42" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O42" s="7">
-        <v>345716</v>
-      </c>
-      <c r="P42" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q42" s="9">
-        <v>46147.625</v>
-      </c>
-      <c r="R42" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S42" s="6" t="s">
-        <v>384</v>
-      </c>
       <c r="T42" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="U42" s="6" t="s">
         <v>65</v>
@@ -8717,19 +8699,19 @@
         <v>0</v>
       </c>
       <c r="AC42" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD42" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE42" s="8">
-        <v>46147.75</v>
+        <v>46150.67013888889</v>
       </c>
       <c r="AF42" s="7">
-        <v>24</v>
+        <v>107165</v>
       </c>
       <c r="AG42" s="9">
-        <v>46147.625</v>
+        <v>46150.583333333336</v>
       </c>
       <c r="AH42" s="6" t="s">
         <v>65</v>
@@ -8741,10 +8723,10 @@
         <v>0</v>
       </c>
       <c r="AK42" s="6" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="AL42" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AM42" s="6" t="s">
         <v>65</v>
@@ -8756,7 +8738,7 @@
         <v>65</v>
       </c>
       <c r="AP42" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ42" s="10" t="s">
         <v>65</v>
@@ -8765,7 +8747,7 @@
         <v>65</v>
       </c>
       <c r="AS42" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AT42" s="7">
         <v>0</v>
@@ -8780,10 +8762,10 @@
         <v>65</v>
       </c>
       <c r="AX42" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY42" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ42" s="6" t="s">
         <v>65</v>
@@ -8795,7 +8777,7 @@
         <v>65</v>
       </c>
       <c r="BC42" s="6" t="s">
-        <v>387</v>
+        <v>87</v>
       </c>
       <c r="BD42" s="10" t="s">
         <v>65</v>
@@ -8804,16 +8786,16 @@
         <v>65</v>
       </c>
       <c r="BF42" s="10">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="BG42" s="10">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="BH42" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="BI42" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="BJ42" s="6" t="s">
         <v>89</v>
@@ -8821,65 +8803,65 @@
     </row>
     <row r="43">
       <c r="A43" s="7">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B43" s="7">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D43" s="8">
-        <v>46153.58720679398</v>
+        <v>45890.75695732639</v>
       </c>
       <c r="E43" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="N43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O43" s="7">
+        <v>287667</v>
+      </c>
+      <c r="P43" s="8">
+        <v>45832.125</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>46153.333333333336</v>
+      </c>
+      <c r="R43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S43" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="T43" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="F43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J43" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M43" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="N43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O43" s="7">
-        <v>346470</v>
-      </c>
-      <c r="P43" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q43" s="9">
-        <v>46150.583333333336</v>
-      </c>
-      <c r="R43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S43" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="T43" s="6" t="s">
-        <v>404</v>
-      </c>
       <c r="U43" s="6" t="s">
         <v>65</v>
       </c>
@@ -8905,19 +8887,19 @@
         <v>0</v>
       </c>
       <c r="AC43" s="6" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="AD43" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE43" s="8">
-        <v>46150.67013888889</v>
+        <v>46153.458333333336</v>
       </c>
       <c r="AF43" s="7">
-        <v>107165</v>
+        <v>120149</v>
       </c>
       <c r="AG43" s="9">
-        <v>46150.583333333336</v>
+        <v>46181.609398148146</v>
       </c>
       <c r="AH43" s="6" t="s">
         <v>65</v>
@@ -8926,37 +8908,37 @@
         <v>78</v>
       </c>
       <c r="AJ43" s="11">
-        <v>0</v>
+        <v>0.012903225806451</v>
       </c>
       <c r="AK43" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL43" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="AM43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AO43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP43" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ43" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS43" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="AL43" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="AM43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP43" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="AQ43" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="AR43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS43" s="6" t="s">
-        <v>411</v>
-      </c>
       <c r="AT43" s="7">
-        <v>0</v>
+        <v>2537</v>
       </c>
       <c r="AU43" s="6" t="s">
         <v>82</v>
@@ -8965,43 +8947,43 @@
         <v>83</v>
       </c>
       <c r="AW43" s="6" t="s">
-        <v>65</v>
+        <v>411</v>
       </c>
       <c r="AX43" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY43" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ43" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA43" s="8">
-        <v>46230.99998842592</v>
+        <v>46209.99998842592</v>
       </c>
       <c r="BB43" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC43" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD43" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE43" s="10" t="s">
-        <v>65</v>
+        <v>412</v>
+      </c>
+      <c r="BD43" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE43" s="10">
+        <v>52700</v>
       </c>
       <c r="BF43" s="10">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="BG43" s="10">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="BH43" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="BI43" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="BJ43" s="6" t="s">
         <v>89</v>
@@ -9009,65 +8991,65 @@
     </row>
     <row r="44">
       <c r="A44" s="7">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B44" s="7">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D44" s="8">
-        <v>45890.75695732639</v>
+        <v>46101.54787534722</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O44" s="7">
+        <v>337543</v>
+      </c>
+      <c r="P44" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q44" s="9">
+        <v>46147.625</v>
+      </c>
+      <c r="R44" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S44" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="T44" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="K44" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M44" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="N44" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O44" s="7">
-        <v>287667</v>
-      </c>
-      <c r="P44" s="8">
-        <v>45832.125</v>
-      </c>
-      <c r="Q44" s="9">
-        <v>46153.333333333336</v>
-      </c>
-      <c r="R44" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S44" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="T44" s="6" t="s">
-        <v>413</v>
-      </c>
       <c r="U44" s="6" t="s">
         <v>65</v>
       </c>
@@ -9084,28 +9066,28 @@
         <v>65</v>
       </c>
       <c r="Z44" s="10">
-        <v>0</v>
+        <v>170.96</v>
       </c>
       <c r="AA44" s="10">
         <v>0</v>
       </c>
       <c r="AB44" s="10">
-        <v>0</v>
+        <v>170.96</v>
       </c>
       <c r="AC44" s="6" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="AD44" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE44" s="8">
-        <v>46153.458333333336</v>
+        <v>46153.75</v>
       </c>
       <c r="AF44" s="7">
-        <v>118640</v>
+        <v>57766</v>
       </c>
       <c r="AG44" s="9">
-        <v>46175.3575</v>
+        <v>46185.45006944444</v>
       </c>
       <c r="AH44" s="6" t="s">
         <v>65</v>
@@ -9114,13 +9096,13 @@
         <v>78</v>
       </c>
       <c r="AJ44" s="11">
-        <v>0.012903225806451</v>
+        <v>0</v>
       </c>
       <c r="AK44" s="6" t="s">
-        <v>136</v>
+        <v>346</v>
       </c>
       <c r="AL44" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM44" s="6" t="s">
         <v>65</v>
@@ -9132,19 +9114,19 @@
         <v>65</v>
       </c>
       <c r="AP44" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="AQ44" s="10">
-        <v>0</v>
+        <v>248</v>
+      </c>
+      <c r="AQ44" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR44" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS44" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AT44" s="7">
-        <v>2349</v>
+        <v>1728</v>
       </c>
       <c r="AU44" s="6" t="s">
         <v>82</v>
@@ -9153,37 +9135,37 @@
         <v>83</v>
       </c>
       <c r="AW44" s="6" t="s">
-        <v>419</v>
+        <v>65</v>
       </c>
       <c r="AX44" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY44" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ44" s="6" t="s">
         <v>65</v>
       </c>
       <c r="BA44" s="8">
-        <v>46209.99998842592</v>
+        <v>46237.99998842592</v>
       </c>
       <c r="BB44" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC44" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="BD44" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE44" s="10">
-        <v>52700</v>
+        <v>347</v>
+      </c>
+      <c r="BD44" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="BE44" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BF44" s="10">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="BG44" s="10">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="BH44" s="6" t="s">
         <v>420</v>
@@ -9197,16 +9179,16 @@
     </row>
     <row r="45">
       <c r="A45" s="7">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="B45" s="7">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>421</v>
       </c>
       <c r="D45" s="8">
-        <v>46101.54787534722</v>
+        <v>46160.53526894676</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>422</v>
@@ -9239,19 +9221,19 @@
         <v>65</v>
       </c>
       <c r="O45" s="7">
-        <v>337543</v>
+        <v>347450</v>
       </c>
       <c r="P45" s="8" t="s">
         <v>65</v>
       </c>
       <c r="Q45" s="9">
-        <v>46147.625</v>
+        <v>46154.333333333336</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S45" s="6" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="T45" s="6" t="s">
         <v>421</v>
@@ -9281,19 +9263,19 @@
         <v>0</v>
       </c>
       <c r="AC45" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD45" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE45" s="8">
-        <v>46153.75</v>
+        <v>46154.458333333336</v>
       </c>
       <c r="AF45" s="7">
-        <v>55000</v>
+        <v>1</v>
       </c>
       <c r="AG45" s="9">
-        <v>46147.625</v>
+        <v>46154.333333333336</v>
       </c>
       <c r="AH45" s="6" t="s">
         <v>65</v>
@@ -9305,7 +9287,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="6" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="AL45" s="6" t="s">
         <v>423</v>
@@ -9320,7 +9302,7 @@
         <v>65</v>
       </c>
       <c r="AP45" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AQ45" s="10" t="s">
         <v>65</v>
@@ -9329,7 +9311,7 @@
         <v>65</v>
       </c>
       <c r="AS45" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AT45" s="7">
         <v>0</v>
@@ -9344,13 +9326,13 @@
         <v>65</v>
       </c>
       <c r="AX45" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY45" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ45" s="6" t="s">
-        <v>65</v>
+        <v>428</v>
       </c>
       <c r="BA45" s="8">
         <v>46237.99998842592</v>
@@ -9359,7 +9341,7 @@
         <v>65</v>
       </c>
       <c r="BC45" s="6" t="s">
-        <v>347</v>
+        <v>386</v>
       </c>
       <c r="BD45" s="10" t="s">
         <v>65</v>
@@ -9368,16 +9350,16 @@
         <v>65</v>
       </c>
       <c r="BF45" s="10">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="BG45" s="10">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="BH45" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="BI45" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="BJ45" s="6" t="s">
         <v>89</v>
@@ -9385,25 +9367,25 @@
     </row>
     <row r="46">
       <c r="A46" s="7">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="B46" s="7">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D46" s="8">
-        <v>46160.53526894676</v>
+        <v>46160.537332175925</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>65</v>
@@ -9412,7 +9394,7 @@
         <v>342</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>342</v>
@@ -9421,28 +9403,28 @@
         <v>65</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O46" s="7">
-        <v>347450</v>
-      </c>
-      <c r="P46" s="8" t="s">
-        <v>65</v>
+        <v>347451</v>
+      </c>
+      <c r="P46" s="8">
+        <v>45061.125</v>
       </c>
       <c r="Q46" s="9">
-        <v>46154.333333333336</v>
+        <v>46157.416666666664</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S46" s="6" t="s">
-        <v>433</v>
+        <v>92</v>
       </c>
       <c r="T46" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="U46" s="6" t="s">
         <v>65</v>
@@ -9460,28 +9442,28 @@
         <v>65</v>
       </c>
       <c r="Z46" s="10">
-        <v>0</v>
+        <v>266.88</v>
       </c>
       <c r="AA46" s="10">
         <v>0</v>
       </c>
       <c r="AB46" s="10">
-        <v>0</v>
+        <v>266.88</v>
       </c>
       <c r="AC46" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD46" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE46" s="8">
-        <v>46154.458333333336</v>
+        <v>46157.541666666664</v>
       </c>
       <c r="AF46" s="7">
-        <v>1</v>
+        <v>216396</v>
       </c>
       <c r="AG46" s="9">
-        <v>46154.333333333336</v>
+        <v>46181.6094212963</v>
       </c>
       <c r="AH46" s="6" t="s">
         <v>65</v>
@@ -9490,13 +9472,13 @@
         <v>78</v>
       </c>
       <c r="AJ46" s="11">
-        <v>0</v>
+        <v>0.015662650602409</v>
       </c>
       <c r="AK46" s="6" t="s">
-        <v>385</v>
+        <v>105</v>
       </c>
       <c r="AL46" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AM46" s="6" t="s">
         <v>65</v>
@@ -9508,19 +9490,19 @@
         <v>65</v>
       </c>
       <c r="AP46" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="AQ46" s="10" t="s">
-        <v>65</v>
+        <v>248</v>
+      </c>
+      <c r="AQ46" s="10">
+        <v>0</v>
       </c>
       <c r="AR46" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS46" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AT46" s="7">
-        <v>0</v>
+        <v>2455</v>
       </c>
       <c r="AU46" s="6" t="s">
         <v>82</v>
@@ -9532,13 +9514,13 @@
         <v>65</v>
       </c>
       <c r="AX46" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY46" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ46" s="6" t="s">
-        <v>435</v>
+        <v>65</v>
       </c>
       <c r="BA46" s="8">
         <v>46237.99998842592</v>
@@ -9547,19 +9529,19 @@
         <v>65</v>
       </c>
       <c r="BC46" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="BD46" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE46" s="10" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="BD46" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE46" s="10">
+        <v>41500</v>
       </c>
       <c r="BF46" s="10">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="BG46" s="10">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="BH46" s="6" t="s">
         <v>436</v>
@@ -9573,16 +9555,16 @@
     </row>
     <row r="47">
       <c r="A47" s="7">
-        <v>2020</v>
+        <v>2027</v>
       </c>
       <c r="B47" s="7">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>437</v>
       </c>
       <c r="D47" s="8">
-        <v>46160.537332175925</v>
+        <v>46160.53851987269</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>438</v>
@@ -9615,19 +9597,19 @@
         <v>65</v>
       </c>
       <c r="O47" s="7">
-        <v>347451</v>
-      </c>
-      <c r="P47" s="8">
-        <v>45061.125</v>
+        <v>347452</v>
+      </c>
+      <c r="P47" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="Q47" s="9">
-        <v>46157.416666666664</v>
+        <v>46158.333333333336</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S47" s="6" t="s">
-        <v>105</v>
+        <v>426</v>
       </c>
       <c r="T47" s="6" t="s">
         <v>437</v>
@@ -9648,28 +9630,28 @@
         <v>65</v>
       </c>
       <c r="Z47" s="10">
-        <v>266.88</v>
+        <v>0</v>
       </c>
       <c r="AA47" s="10">
         <v>0</v>
       </c>
       <c r="AB47" s="10">
-        <v>266.88</v>
+        <v>0</v>
       </c>
       <c r="AC47" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD47" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE47" s="8">
-        <v>46157.541666666664</v>
+        <v>46158.458333333336</v>
       </c>
       <c r="AF47" s="7">
-        <v>216088</v>
+        <v>1</v>
       </c>
       <c r="AG47" s="9">
-        <v>46176.428391203706</v>
+        <v>46158.333333333336</v>
       </c>
       <c r="AH47" s="6" t="s">
         <v>65</v>
@@ -9678,10 +9660,10 @@
         <v>78</v>
       </c>
       <c r="AJ47" s="11">
-        <v>0.015662650602409</v>
+        <v>0</v>
       </c>
       <c r="AK47" s="6" t="s">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="AL47" s="6" t="s">
         <v>439</v>
@@ -9696,10 +9678,10 @@
         <v>65</v>
       </c>
       <c r="AP47" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="AQ47" s="10">
-        <v>0</v>
+        <v>248</v>
+      </c>
+      <c r="AQ47" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="AR47" s="6" t="s">
         <v>65</v>
@@ -9708,7 +9690,7 @@
         <v>442</v>
       </c>
       <c r="AT47" s="7">
-        <v>3849</v>
+        <v>0</v>
       </c>
       <c r="AU47" s="6" t="s">
         <v>82</v>
@@ -9720,13 +9702,13 @@
         <v>65</v>
       </c>
       <c r="AX47" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY47" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ47" s="6" t="s">
-        <v>65</v>
+        <v>428</v>
       </c>
       <c r="BA47" s="8">
         <v>46237.99998842592</v>
@@ -9735,19 +9717,19 @@
         <v>65</v>
       </c>
       <c r="BC47" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD47" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE47" s="10">
-        <v>41500</v>
+        <v>386</v>
+      </c>
+      <c r="BD47" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="BE47" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="BF47" s="10">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="BG47" s="10">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="BH47" s="6" t="s">
         <v>443</v>
@@ -9761,16 +9743,16 @@
     </row>
     <row r="48">
       <c r="A48" s="7">
-        <v>2027</v>
+        <v>2021</v>
       </c>
       <c r="B48" s="7">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>444</v>
       </c>
       <c r="D48" s="8">
-        <v>46160.53851987269</v>
+        <v>46003.72969502315</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>445</v>
@@ -9785,13 +9767,13 @@
         <v>65</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>342</v>
+        <v>255</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>447</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>342</v>
+        <v>255</v>
       </c>
       <c r="L48" s="6" t="s">
         <v>65</v>
@@ -9803,19 +9785,19 @@
         <v>65</v>
       </c>
       <c r="O48" s="7">
-        <v>347452</v>
-      </c>
-      <c r="P48" s="8" t="s">
-        <v>65</v>
+        <v>320775</v>
+      </c>
+      <c r="P48" s="8">
+        <v>36526.083333333336</v>
       </c>
       <c r="Q48" s="9">
-        <v>46158.333333333336</v>
+        <v>46160.336805555555</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>65</v>
       </c>
       <c r="S48" s="6" t="s">
-        <v>433</v>
+        <v>92</v>
       </c>
       <c r="T48" s="6" t="s">
         <v>444</v>
@@ -9836,28 +9818,28 @@
         <v>65</v>
       </c>
       <c r="Z48" s="10">
-        <v>0</v>
+        <v>280.3</v>
       </c>
       <c r="AA48" s="10">
         <v>0</v>
       </c>
       <c r="AB48" s="10">
-        <v>0</v>
+        <v>280.3</v>
       </c>
       <c r="AC48" s="6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AD48" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE48" s="8">
-        <v>46158.458333333336</v>
+        <v>46160.461805555555</v>
       </c>
       <c r="AF48" s="7">
-        <v>1</v>
+        <v>30085</v>
       </c>
       <c r="AG48" s="9">
-        <v>46158.333333333336</v>
+        <v>46181.6094212963</v>
       </c>
       <c r="AH48" s="6" t="s">
         <v>65</v>
@@ -9866,10 +9848,10 @@
         <v>78</v>
       </c>
       <c r="AJ48" s="11">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="AK48" s="6" t="s">
-        <v>385</v>
+        <v>449</v>
       </c>
       <c r="AL48" s="6" t="s">
         <v>446</v>
@@ -9884,19 +9866,19 @@
         <v>65</v>
       </c>
       <c r="AP48" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="AQ48" s="10" t="s">
-        <v>65</v>
+        <v>178</v>
+      </c>
+      <c r="AQ48" s="10">
+        <v>0</v>
       </c>
       <c r="AR48" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AS48" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AT48" s="7">
-        <v>0</v>
+        <v>-139045</v>
       </c>
       <c r="AU48" s="6" t="s">
         <v>82</v>
@@ -9905,43 +9887,43 @@
         <v>83</v>
       </c>
       <c r="AW48" s="6" t="s">
-        <v>65</v>
+        <v>451</v>
       </c>
       <c r="AX48" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY48" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ48" s="6" t="s">
-        <v>435</v>
+        <v>65</v>
       </c>
       <c r="BA48" s="8">
-        <v>46237.99998842592</v>
+        <v>46216.99998842592</v>
       </c>
       <c r="BB48" s="9" t="s">
         <v>65</v>
       </c>
       <c r="BC48" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="BD48" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE48" s="10" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="BD48" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE48" s="10">
+        <v>1</v>
       </c>
       <c r="BF48" s="10">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="BG48" s="10">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="BH48" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="BI48" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="BJ48" s="6" t="s">
         <v>89</v>
@@ -9949,65 +9931,65 @@
     </row>
     <row r="49">
       <c r="A49" s="7">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B49" s="7">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D49" s="8">
-        <v>46003.72969502315</v>
+        <v>46057.51524019676</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G49" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M49" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="N49" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O49" s="7">
+        <v>329595</v>
+      </c>
+      <c r="P49" s="8">
+        <v>45934.125</v>
+      </c>
+      <c r="Q49" s="9">
+        <v>46160.375</v>
+      </c>
+      <c r="R49" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S49" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="T49" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="H49" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J49" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="K49" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M49" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="N49" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O49" s="7">
-        <v>320775</v>
-      </c>
-      <c r="P49" s="8">
-        <v>36526.083333333336</v>
-      </c>
-      <c r="Q49" s="9">
-        <v>46160.336805555555</v>
-      </c>
-      <c r="R49" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S49" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="T49" s="6" t="s">
-        <v>451</v>
-      </c>
       <c r="U49" s="6" t="s">
         <v>65</v>
       </c>
@@ -10024,28 +10006,28 @@
         <v>65</v>
       </c>
       <c r="Z49" s="10">
-        <v>280.3</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="10">
         <v>0</v>
       </c>
       <c r="AB49" s="10">
-        <v>280.3</v>
+        <v>0</v>
       </c>
       <c r="AC49" s="6" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="AD49" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AE49" s="8">
-        <v>46160.461805555555</v>
+        <v>46160.5</v>
       </c>
       <c r="AF49" s="7">
-        <v>193340</v>
+        <v>135595</v>
       </c>
       <c r="AG49" s="9">
-        <v>46176.39202546296</v>
+        <v>46181.60940972222</v>
       </c>
       <c r="AH49" s="6" t="s">
         <v>65</v>
@@ -10054,13 +10036,13 @@
         <v>78</v>
       </c>
       <c r="AJ49" s="11">
-        <v>630</v>
+        <v>0.013359528487229</v>
       </c>
       <c r="AK49" s="6" t="s">
-        <v>456</v>
+        <v>138</v>
       </c>
       <c r="AL49" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AM49" s="6" t="s">
         <v>65</v>
@@ -10072,7 +10054,7 @@
         <v>65</v>
       </c>
       <c r="AP49" s="6" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="AQ49" s="10">
         <v>0</v>
@@ -10081,10 +10063,10 @@
         <v>65</v>
       </c>
       <c r="AS49" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AT49" s="7">
-        <v>907</v>
+        <v>2132</v>
       </c>
       <c r="AU49" s="6" t="s">
         <v>82</v>
@@ -10093,13 +10075,13 @@
         <v>83</v>
       </c>
       <c r="AW49" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AX49" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY49" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ49" s="6" t="s">
         <v>65</v>
@@ -10111,287 +10093,99 @@
         <v>65</v>
       </c>
       <c r="BC49" s="6" t="s">
-        <v>87</v>
+        <v>412</v>
       </c>
       <c r="BD49" s="10">
         <v>0</v>
       </c>
       <c r="BE49" s="10">
-        <v>1</v>
+        <v>50900</v>
       </c>
       <c r="BF49" s="10">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="BG49" s="10">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="BH49" s="6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="BI49" s="6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="BJ49" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="7">
-        <v>2023</v>
-      </c>
-      <c r="B50" s="7">
-        <v>2022</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D50" s="8">
-        <v>46057.51524019676</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M50" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="N50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O50" s="7">
-        <v>329595</v>
-      </c>
-      <c r="P50" s="8">
-        <v>45934.125</v>
-      </c>
-      <c r="Q50" s="9">
-        <v>46160.375</v>
-      </c>
-      <c r="R50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S50" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="T50" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="U50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="V50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="W50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="X50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z50" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA50" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB50" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC50" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AD50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE50" s="8">
-        <v>46160.5</v>
-      </c>
-      <c r="AF50" s="7">
-        <v>134362</v>
-      </c>
-      <c r="AG50" s="9">
-        <v>46175.357511574075</v>
-      </c>
-      <c r="AH50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AI50" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ50" s="11">
-        <v>0.013359528487229</v>
-      </c>
-      <c r="AK50" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="AL50" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="AM50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP50" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="AQ50" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS50" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="AT50" s="7">
-        <v>2003</v>
-      </c>
-      <c r="AU50" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="AV50" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW50" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="AX50" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY50" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AZ50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="BA50" s="8">
-        <v>46216.99998842592</v>
-      </c>
-      <c r="BB50" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="BC50" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="BD50" s="10">
-        <v>0</v>
-      </c>
-      <c r="BE50" s="10">
-        <v>50900</v>
-      </c>
-      <c r="BF50" s="10">
-        <v>680</v>
-      </c>
-      <c r="BG50" s="10">
-        <v>680</v>
-      </c>
-      <c r="BH50" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="BI50" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="BJ50" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="51" ht="23" customHeight="1">
-      <c r="A51" s="13"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
-      <c r="L51" s="12"/>
-      <c r="M51" s="12"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="14"/>
-      <c r="Q51" s="15"/>
-      <c r="R51" s="12"/>
-      <c r="S51" s="12"/>
-      <c r="T51" s="12"/>
-      <c r="U51" s="12"/>
-      <c r="V51" s="12"/>
-      <c r="W51" s="12"/>
-      <c r="X51" s="12"/>
-      <c r="Y51" s="12"/>
-      <c r="Z51" s="16">
-        <f>SUM(Z6:Z50)</f>
-      </c>
-      <c r="AA51" s="16">
-        <f>SUM(AA6:AA50)</f>
-      </c>
-      <c r="AB51" s="16">
-        <f>SUM(AB6:AB50)</f>
-      </c>
-      <c r="AC51" s="12"/>
-      <c r="AD51" s="12"/>
-      <c r="AE51" s="14"/>
-      <c r="AF51" s="13"/>
-      <c r="AG51" s="15"/>
-      <c r="AH51" s="12"/>
-      <c r="AI51" s="12"/>
-      <c r="AJ51" s="17"/>
-      <c r="AK51" s="12"/>
-      <c r="AL51" s="12"/>
-      <c r="AM51" s="12"/>
-      <c r="AN51" s="12"/>
-      <c r="AO51" s="12"/>
-      <c r="AP51" s="12"/>
-      <c r="AQ51" s="16"/>
-      <c r="AR51" s="12"/>
-      <c r="AS51" s="12"/>
-      <c r="AT51" s="13"/>
-      <c r="AU51" s="12"/>
-      <c r="AV51" s="12"/>
-      <c r="AW51" s="12"/>
-      <c r="AX51" s="12"/>
-      <c r="AY51" s="12"/>
-      <c r="AZ51" s="12"/>
-      <c r="BA51" s="14"/>
-      <c r="BB51" s="15"/>
-      <c r="BC51" s="12"/>
-      <c r="BD51" s="16"/>
-      <c r="BE51" s="16"/>
-      <c r="BF51" s="16"/>
-      <c r="BG51" s="16"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51" s="12"/>
-      <c r="BJ51" s="12"/>
+    <row r="50" ht="23" customHeight="1">
+      <c r="A50" s="13"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+      <c r="L50" s="12"/>
+      <c r="M50" s="12"/>
+      <c r="N50" s="12"/>
+      <c r="O50" s="13"/>
+      <c r="P50" s="14"/>
+      <c r="Q50" s="15"/>
+      <c r="R50" s="12"/>
+      <c r="S50" s="12"/>
+      <c r="T50" s="12"/>
+      <c r="U50" s="12"/>
+      <c r="V50" s="12"/>
+      <c r="W50" s="12"/>
+      <c r="X50" s="12"/>
+      <c r="Y50" s="12"/>
+      <c r="Z50" s="16">
+        <f>SUM(Z6:Z49)</f>
+      </c>
+      <c r="AA50" s="16">
+        <f>SUM(AA6:AA49)</f>
+      </c>
+      <c r="AB50" s="16">
+        <f>SUM(AB6:AB49)</f>
+      </c>
+      <c r="AC50" s="12"/>
+      <c r="AD50" s="12"/>
+      <c r="AE50" s="14"/>
+      <c r="AF50" s="13"/>
+      <c r="AG50" s="15"/>
+      <c r="AH50" s="12"/>
+      <c r="AI50" s="12"/>
+      <c r="AJ50" s="17"/>
+      <c r="AK50" s="12"/>
+      <c r="AL50" s="12"/>
+      <c r="AM50" s="12"/>
+      <c r="AN50" s="12"/>
+      <c r="AO50" s="12"/>
+      <c r="AP50" s="12"/>
+      <c r="AQ50" s="16"/>
+      <c r="AR50" s="12"/>
+      <c r="AS50" s="12"/>
+      <c r="AT50" s="13"/>
+      <c r="AU50" s="12"/>
+      <c r="AV50" s="12"/>
+      <c r="AW50" s="12"/>
+      <c r="AX50" s="12"/>
+      <c r="AY50" s="12"/>
+      <c r="AZ50" s="12"/>
+      <c r="BA50" s="14"/>
+      <c r="BB50" s="15"/>
+      <c r="BC50" s="12"/>
+      <c r="BD50" s="16"/>
+      <c r="BE50" s="16"/>
+      <c r="BF50" s="16"/>
+      <c r="BG50" s="16"/>
+      <c r="BH50" s="12"/>
+      <c r="BI50" s="12"/>
+      <c r="BJ50" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:BJ5"/>
